--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -25,6 +25,7 @@
     <sheet name="Sanban" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Lists" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Assets" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Text" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -37,7 +38,7 @@
     <numFmt numFmtId="164" formatCode="0.00\x"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -184,6 +185,9 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -289,7 +293,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -518,6 +522,10 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -9258,6 +9266,446 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="43" min="1" max="1"/>
+    <col width="34" customWidth="1" style="43" min="2" max="2"/>
+    <col width="52" customWidth="1" style="43" min="3" max="3"/>
+    <col width="16" customWidth="1" style="43" min="4" max="4"/>
+    <col width="66" customWidth="1" style="43" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="77" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D1" s="77" t="inlineStr">
+        <is>
+          <t>Placeholders</t>
+        </is>
+      </c>
+      <c r="E1" s="77" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>outcome.carried</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>End of stage — title</t>
+        </is>
+      </c>
+      <c r="C2" s="78" t="inlineStr">
+        <is>
+          <t>Carried</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" s="78" t="inlineStr">
+        <is>
+          <t>The title when you win a stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>outcome.defeated</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>End of stage — title</t>
+        </is>
+      </c>
+      <c r="C3" s="78" t="inlineStr">
+        <is>
+          <t>Defeated</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" s="78" t="inlineStr">
+        <is>
+          <t>The title when you lose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>outcome.no_decision</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>End of stage — title</t>
+        </is>
+      </c>
+      <c r="C4" s="78" t="inlineStr">
+        <is>
+          <t>No decision</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" s="78" t="inlineStr">
+        <is>
+          <t>The title when the turn limit ran out with no result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>outcome.conference_over</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>End of stage — title</t>
+        </is>
+      </c>
+      <c r="C5" s="78" t="inlineStr">
+        <is>
+          <t>Conference over</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" s="78" t="inlineStr">
+        <is>
+          <t>Instead of Carried, where the room was a press conference and nobody was beaten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>outcome.closed</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>End of stage — title</t>
+        </is>
+      </c>
+      <c r="C6" s="78" t="inlineStr">
+        <is>
+          <t>{stage} closed</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="E6" s="78" t="inlineStr">
+        <is>
+          <t>For a room that is scored rather than won: the caucus, the town hall, the TV debate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>outcome.closed_unnamed</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>End of stage — title</t>
+        </is>
+      </c>
+      <c r="C7" s="78" t="inlineStr">
+        <is>
+          <t>It closed</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" s="78" t="inlineStr">
+        <is>
+          <t>The same line where the stage has no name to use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>outcome.ahead</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>End of stage — what it was worth</t>
+        </is>
+      </c>
+      <c r="C8" s="78" t="inlineStr">
+        <is>
+          <t>You start {count} ahead at the floor debate.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E8" s="78" t="inlineStr">
+        <is>
+          <t>Shown when this stage's score carries into a later one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>outcome.behind</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>End of stage — what it was worth</t>
+        </is>
+      </c>
+      <c r="C9" s="78" t="inlineStr">
+        <is>
+          <t>You start {count} behind at the floor debate.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E9" s="78" t="inlineStr">
+        <is>
+          <t>The same, where the score went against you. {count} is already positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>outcome.pleased</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>End of stage — what it was worth</t>
+        </is>
+      </c>
+      <c r="C10" s="78" t="inlineStr">
+        <is>
+          <t>Pleased: {names}.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>names</t>
+        </is>
+      </c>
+      <c r="E10" s="78" t="inlineStr">
+        <is>
+          <t>Which organisations your answers pleased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>outcome.no_rewards</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>End of stage — what it was worth</t>
+        </is>
+      </c>
+      <c r="C11" s="78" t="inlineStr">
+        <is>
+          <t>This stage has no rewards set yet.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" s="78" t="inlineStr">
+        <is>
+          <t>The truth, rather than silence that reads as a bug. Every playtest stage says this until its numbers are set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>outcome.xp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>End of stage — what it was worth</t>
+        </is>
+      </c>
+      <c r="C12" s="78" t="inlineStr">
+        <is>
+          <t>{count} XP</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E12" s="78" t="inlineStr">
+        <is>
+          <t>Listed alongside the standings that moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>outcome.sign_off_unwritten</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>End of stage — last stage of a level</t>
+        </is>
+      </c>
+      <c r="C13" s="78" t="inlineStr">
+        <is>
+          <t>That is the end of it.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" s="78" t="inlineStr">
+        <is>
+          <t>Used when a level has no win_text or loss_text of its own AND no name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>outcome.sign_off_named</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>End of stage — last stage of a level</t>
+        </is>
+      </c>
+      <c r="C14" s="78" t="inlineStr">
+        <is>
+          <t>{level} is behind you.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E14" s="78" t="inlineStr">
+        <is>
+          <t>Used when a level has no win_text or loss_text written yet. True of any level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>outcome.close</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>End of stage — button</t>
+        </is>
+      </c>
+      <c r="C15" s="78" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" s="78" t="inlineStr">
+        <is>
+          <t>The button when you are not in a level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>outcome.back_to_office</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>End of stage — button</t>
+        </is>
+      </c>
+      <c r="C16" s="78" t="inlineStr">
+        <is>
+          <t>Back to the Office</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" s="78" t="inlineStr">
+        <is>
+          <t>The button after the last stage of a level, or after a loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>outcome.next_stage</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>End of stage — button</t>
+        </is>
+      </c>
+      <c r="C17" s="78" t="inlineStr">
+        <is>
+          <t>On to the next stage</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" s="78" t="inlineStr">
+        <is>
+          <t>The button when the level has another room waiting.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
@@ -9462,15 +9910,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B15" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="42" t="inlineStr">
         <is>
           <t>XP to unlock — placeholder</t>
         </is>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -9272,7 +9272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="43" min="1" max="1"/>
@@ -9310,12 +9310,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>outcome.carried</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>End of stage — title</t>
         </is>
@@ -9325,7 +9325,7 @@
           <t>Carried</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="42" t="inlineStr"/>
       <c r="E2" s="78" t="inlineStr">
         <is>
           <t>The title when you win a stage.</t>
@@ -9333,12 +9333,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>outcome.defeated</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>End of stage — title</t>
         </is>
@@ -9348,7 +9348,7 @@
           <t>Defeated</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" s="42" t="inlineStr"/>
       <c r="E3" s="78" t="inlineStr">
         <is>
           <t>The title when you lose.</t>
@@ -9356,12 +9356,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="42" t="inlineStr">
         <is>
           <t>outcome.no_decision</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>End of stage — title</t>
         </is>
@@ -9371,7 +9371,7 @@
           <t>No decision</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="42" t="inlineStr"/>
       <c r="E4" s="78" t="inlineStr">
         <is>
           <t>The title when the turn limit ran out with no result.</t>
@@ -9379,12 +9379,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="42" t="inlineStr">
         <is>
           <t>outcome.conference_over</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>End of stage — title</t>
         </is>
@@ -9394,7 +9394,7 @@
           <t>Conference over</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" s="42" t="inlineStr"/>
       <c r="E5" s="78" t="inlineStr">
         <is>
           <t>Instead of Carried, where the room was a press conference and nobody was beaten.</t>
@@ -9402,12 +9402,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>outcome.closed</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>End of stage — title</t>
         </is>
@@ -9417,7 +9417,7 @@
           <t>{stage} closed</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
@@ -9429,12 +9429,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="42" t="inlineStr">
         <is>
           <t>outcome.closed_unnamed</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>End of stage — title</t>
         </is>
@@ -9444,7 +9444,7 @@
           <t>It closed</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" s="42" t="inlineStr"/>
       <c r="E7" s="78" t="inlineStr">
         <is>
           <t>The same line where the stage has no name to use.</t>
@@ -9452,12 +9452,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>outcome.ahead</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>End of stage — what it was worth</t>
         </is>
@@ -9467,7 +9467,7 @@
           <t>You start {count} ahead at the floor debate.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -9479,12 +9479,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>outcome.behind</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>End of stage — what it was worth</t>
         </is>
@@ -9494,7 +9494,7 @@
           <t>You start {count} behind at the floor debate.</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -9506,12 +9506,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>outcome.pleased</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>End of stage — what it was worth</t>
         </is>
@@ -9521,7 +9521,7 @@
           <t>Pleased: {names}.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>names</t>
         </is>
@@ -9533,12 +9533,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>outcome.no_rewards</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="42" t="inlineStr">
         <is>
           <t>End of stage — what it was worth</t>
         </is>
@@ -9548,7 +9548,7 @@
           <t>This stage has no rewards set yet.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" s="42" t="inlineStr"/>
       <c r="E11" s="78" t="inlineStr">
         <is>
           <t>The truth, rather than silence that reads as a bug. Every playtest stage says this until its numbers are set.</t>
@@ -9556,12 +9556,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>outcome.xp</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>End of stage — what it was worth</t>
         </is>
@@ -9571,7 +9571,7 @@
           <t>{count} XP</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -9583,12 +9583,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>outcome.sign_off_unwritten</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="42" t="inlineStr">
         <is>
           <t>End of stage — last stage of a level</t>
         </is>
@@ -9598,7 +9598,7 @@
           <t>That is the end of it.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" s="42" t="inlineStr"/>
       <c r="E13" s="78" t="inlineStr">
         <is>
           <t>Used when a level has no win_text or loss_text of its own AND no name.</t>
@@ -9606,12 +9606,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>outcome.sign_off_named</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>End of stage — last stage of a level</t>
         </is>
@@ -9621,7 +9621,7 @@
           <t>{level} is behind you.</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>level</t>
         </is>
@@ -9633,12 +9633,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>outcome.close</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>End of stage — button</t>
         </is>
@@ -9648,7 +9648,7 @@
           <t>Close</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" s="42" t="inlineStr"/>
       <c r="E15" s="78" t="inlineStr">
         <is>
           <t>The button when you are not in a level.</t>
@@ -9656,12 +9656,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>outcome.back_to_office</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>End of stage — button</t>
         </is>
@@ -9671,7 +9671,7 @@
           <t>Back to the Office</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" s="42" t="inlineStr"/>
       <c r="E16" s="78" t="inlineStr">
         <is>
           <t>The button after the last stage of a level, or after a loss.</t>
@@ -9679,12 +9679,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>outcome.next_stage</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>End of stage — button</t>
         </is>
@@ -9694,10 +9694,937 @@
           <t>On to the next stage</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" s="42" t="inlineStr"/>
       <c r="E17" s="78" t="inlineStr">
         <is>
           <t>The button when the level has another room waiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="inlineStr">
+        <is>
+          <t>battle.no_stage</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>Battle — notices</t>
+        </is>
+      </c>
+      <c r="C18" s="78" t="inlineStr">
+        <is>
+          <t>There is no stage to play here.</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr"/>
+      <c r="E18" s="78" t="inlineStr">
+        <is>
+          <t>Shown if a stage cannot be found at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>battle.cannot_start</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>Battle — notices</t>
+        </is>
+      </c>
+      <c r="C19" s="78" t="inlineStr">
+        <is>
+          <t>This battle could not start:
+• {problems}</t>
+        </is>
+      </c>
+      <c r="D19" s="42" t="inlineStr">
+        <is>
+          <t>problems</t>
+        </is>
+      </c>
+      <c r="E19" s="78" t="inlineStr">
+        <is>
+          <t>{problems} is a bulleted list the game fills in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>battle.card_refused</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>Battle — notices</t>
+        </is>
+      </c>
+      <c r="C20" s="78" t="inlineStr">
+        <is>
+          <t>That card cannot be played.</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr"/>
+      <c r="E20" s="78" t="inlineStr">
+        <is>
+          <t>A fallback; the engine usually gives its own reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>battle.declined</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>Battle — notices</t>
+        </is>
+      </c>
+      <c r="C21" s="78" t="inlineStr">
+        <is>
+          <t>You let that one go. The room cools.</t>
+        </is>
+      </c>
+      <c r="D21" s="42" t="inlineStr"/>
+      <c r="E21" s="78" t="inlineStr">
+        <is>
+          <t>Ending a turn without answering the question in front of you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="inlineStr">
+        <is>
+          <t>battle.passed</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>Battle — notices</t>
+        </is>
+      </c>
+      <c r="C22" s="78" t="inlineStr">
+        <is>
+          <t>You said nothing. One less energy this turn.</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr"/>
+      <c r="E22" s="78" t="inlineStr">
+        <is>
+          <t>Ending a turn having played no cards, outside a press conference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>narration.sentence</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C23" s="78" t="inlineStr">
+        <is>
+          <t>{who}: {clauses}.</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>who, clauses</t>
+        </is>
+      </c>
+      <c r="E23" s="78" t="inlineStr">
+        <is>
+          <t>The frame the opponent's move is reported in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>narration.they</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C24" s="78" t="inlineStr">
+        <is>
+          <t>They</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr"/>
+      <c r="E24" s="78" t="inlineStr">
+        <is>
+          <t>Stands in for an opponent with no name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>narration.that_opponent</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C25" s="78" t="inlineStr">
+        <is>
+          <t>That opponent</t>
+        </is>
+      </c>
+      <c r="D25" s="42" t="inlineStr"/>
+      <c r="E25" s="78" t="inlineStr">
+        <is>
+          <t>Stands in for a finished opponent with no name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>narration.the_next</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C26" s="78" t="inlineStr">
+        <is>
+          <t>the next</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr"/>
+      <c r="E26" s="78" t="inlineStr">
+        <is>
+          <t>Stands in for the next opponent up, unnamed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>narration.a_member</t>
+        </is>
+      </c>
+      <c r="B27" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C27" s="78" t="inlineStr">
+        <is>
+          <t>a member</t>
+        </is>
+      </c>
+      <c r="D27" s="42" t="inlineStr"/>
+      <c r="E27" s="78" t="inlineStr">
+        <is>
+          <t>Stands in for a committee member with no name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>narration.them_generic</t>
+        </is>
+      </c>
+      <c r="B28" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C28" s="78" t="inlineStr">
+        <is>
+          <t>them</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr"/>
+      <c r="E28" s="78" t="inlineStr">
+        <is>
+          <t>Used where the opponent has no name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>narration.their_generic</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C29" s="78" t="inlineStr">
+        <is>
+          <t>their</t>
+        </is>
+      </c>
+      <c r="D29" s="42" t="inlineStr"/>
+      <c r="E29" s="78" t="inlineStr">
+        <is>
+          <t>Possessive, where the opponent has no name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>narration.their_named</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>Battle — what happened</t>
+        </is>
+      </c>
+      <c r="C30" s="78" t="inlineStr">
+        <is>
+          <t>{name}'s</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E30" s="78" t="inlineStr">
+        <is>
+          <t>Possessive, where they do have a name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>narration.guard_stopped</t>
+        </is>
+      </c>
+      <c r="B31" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C31" s="78" t="inlineStr">
+        <is>
+          <t>{who} guard stopped {count}</t>
+        </is>
+      </c>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>who, count</t>
+        </is>
+      </c>
+      <c r="E31" s="78" t="inlineStr">
+        <is>
+          <t>{who} is already possessive: "Ito's" or "their".</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
+        <is>
+          <t>narration.argued_away</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C32" s="78" t="inlineStr">
+        <is>
+          <t>{amount} argued away from {whom}</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>amount, whom</t>
+        </is>
+      </c>
+      <c r="E32" s="78" t="inlineStr">
+        <is>
+          <t>{amount} already carries its unit: "3 seats", "5%".</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>narration.gaffe.one</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C33" s="78" t="inlineStr">
+        <is>
+          <t>{count} gaffe on your record</t>
+        </is>
+      </c>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E33" s="78" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
+        <is>
+          <t>narration.gaffe.other</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C34" s="78" t="inlineStr">
+        <is>
+          <t>{count} gaffes on your record</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E34" s="78" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="inlineStr">
+        <is>
+          <t>narration.won_over</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C35" s="78" t="inlineStr">
+        <is>
+          <t>{amount} won over</t>
+        </is>
+      </c>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E35" s="78" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>narration.won_over_detail</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C36" s="78" t="inlineStr">
+        <is>
+          <t>{clause} — {detail}</t>
+        </is>
+      </c>
+      <c r="D36" s="42" t="inlineStr">
+        <is>
+          <t>clause, detail</t>
+        </is>
+      </c>
+      <c r="E36" s="78" t="inlineStr">
+        <is>
+          <t>Joins the win to who those people were.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="inlineStr">
+        <is>
+          <t>narration.raised</t>
+        </is>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C37" s="78" t="inlineStr">
+        <is>
+          <t>{unit} raised by {count}</t>
+        </is>
+      </c>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>unit, count</t>
+        </is>
+      </c>
+      <c r="E37" s="78" t="inlineStr">
+        <is>
+          <t>For a room with a mood rather than people: press tone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>narration.unmoved</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C38" s="78" t="inlineStr">
+        <is>
+          <t>{unit} did not move</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E38" s="78" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>narration.short.one</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C39" s="78" t="inlineStr">
+        <is>
+          <t>, {count} point short of the next</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E39" s="78" t="inlineStr">
+        <is>
+          <t>Points that cannot pay for the next person are lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>narration.short.other</t>
+        </is>
+      </c>
+      <c r="B40" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C40" s="78" t="inlineStr">
+        <is>
+          <t>, {count} points short of the next</t>
+        </is>
+      </c>
+      <c r="D40" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E40" s="78" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>narration.all_off</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C41" s="78" t="inlineStr">
+        <is>
+          <t>all of them off {whom}</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>whom</t>
+        </is>
+      </c>
+      <c r="E41" s="78" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="inlineStr">
+        <is>
+          <t>narration.split</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C42" s="78" t="inlineStr">
+        <is>
+          <t>{undecided} from the undecided, {count} off {whom}</t>
+        </is>
+      </c>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>undecided, count, whom</t>
+        </is>
+      </c>
+      <c r="E42" s="78" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>narration.bout_finished</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C43" s="78" t="inlineStr">
+        <is>
+          <t>{who} is finished</t>
+        </is>
+      </c>
+      <c r="D43" s="42" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="E43" s="78" t="inlineStr">
+        <is>
+          <t>The last opponent in the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="inlineStr">
+        <is>
+          <t>narration.bout_finished_next</t>
+        </is>
+      </c>
+      <c r="B44" s="42" t="inlineStr">
+        <is>
+          <t>Battle — your card</t>
+        </is>
+      </c>
+      <c r="C44" s="78" t="inlineStr">
+        <is>
+          <t>{who} is finished — {next} rises</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>who, next</t>
+        </is>
+      </c>
+      <c r="E44" s="78" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="inlineStr">
+        <is>
+          <t>narration.absorbed</t>
+        </is>
+      </c>
+      <c r="B45" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C45" s="78" t="inlineStr">
+        <is>
+          <t>your guard absorbed {count}</t>
+        </is>
+      </c>
+      <c r="D45" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E45" s="78" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>narration.taken</t>
+        </is>
+      </c>
+      <c r="B46" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C46" s="78" t="inlineStr">
+        <is>
+          <t>{amount} taken from you</t>
+        </is>
+      </c>
+      <c r="D46" s="42" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E46" s="78" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="inlineStr">
+        <is>
+          <t>narration.nothing_through</t>
+        </is>
+      </c>
+      <c r="B47" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C47" s="78" t="inlineStr">
+        <is>
+          <t>nothing got through</t>
+        </is>
+      </c>
+      <c r="D47" s="42" t="inlineStr"/>
+      <c r="E47" s="78" t="inlineStr">
+        <is>
+          <t>Their attack was entirely absorbed by your guard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="inlineStr">
+        <is>
+          <t>narration.nothing_to_take</t>
+        </is>
+      </c>
+      <c r="B48" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C48" s="78" t="inlineStr">
+        <is>
+          <t>the attack found nothing to take</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="inlineStr"/>
+      <c r="E48" s="78" t="inlineStr">
+        <is>
+          <t>They attacked and you had nothing left to lose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="inlineStr">
+        <is>
+          <t>narration.gain_none</t>
+        </is>
+      </c>
+      <c r="B49" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C49" s="78" t="inlineStr">
+        <is>
+          <t>{who} pressed the case and won nobody over.</t>
+        </is>
+      </c>
+      <c r="D49" s="42" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="E49" s="78" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>narration.guard_built</t>
+        </is>
+      </c>
+      <c r="B50" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C50" s="78" t="inlineStr">
+        <is>
+          <t>developed {count} guard</t>
+        </is>
+      </c>
+      <c r="D50" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E50" s="78" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="inlineStr">
+        <is>
+          <t>narration.block_none</t>
+        </is>
+      </c>
+      <c r="B51" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C51" s="78" t="inlineStr">
+        <is>
+          <t>{who} could not guard any further.</t>
+        </is>
+      </c>
+      <c r="D51" s="42" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="E51" s="78" t="inlineStr">
+        <is>
+          <t>Their guard is already at the ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="inlineStr">
+        <is>
+          <t>narration.leaned</t>
+        </is>
+      </c>
+      <c r="B52" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C52" s="78" t="inlineStr">
+        <is>
+          <t>leaned on {member}, {count} against you</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>member, count</t>
+        </is>
+      </c>
+      <c r="E52" s="78" t="inlineStr">
+        <is>
+          <t>A committee chair pushing one member away from you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>narration.lean_none</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C53" s="78" t="inlineStr">
+        <is>
+          <t>{who} leaned on the panel and moved nobody.</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="E53" s="78" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="inlineStr">
+        <is>
+          <t>narration.waited</t>
+        </is>
+      </c>
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C54" s="78" t="inlineStr">
+        <is>
+          <t>{who} waited.</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>who</t>
+        </is>
+      </c>
+      <c r="E54" s="78" t="inlineStr">
+        <is>
+          <t>Their move was worth nothing, so they did nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>narration.won_over_them</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Battle — their move</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>won over {amount}</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>The OPPONENT winning people over. The player's version is narration.won_over, which puts the number first.</t>
         </is>
       </c>
     </row>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -9272,7 +9272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="43" min="1" max="1"/>
@@ -10602,31 +10602,762 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>narration.won_over_them</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="42" t="inlineStr">
         <is>
           <t>Battle — their move</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="78" t="inlineStr">
         <is>
           <t>won over {amount}</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="42" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="78" t="inlineStr">
         <is>
           <t>The OPPONENT winning people over. The player's version is narration.won_over, which puts the number first.</t>
         </is>
       </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>brief.heading</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C56" s="78" t="inlineStr">
+        <is>
+          <t>How this room works</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="78" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>brief.bullet</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C57" s="78" t="inlineStr">
+        <is>
+          <t>• {label} — {detail}</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>label, detail</t>
+        </is>
+      </c>
+      <c r="E57" s="78" t="inlineStr">
+        <is>
+          <t>The shape of every line in the list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>brief.label.turns</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C58" s="78" t="inlineStr">
+        <is>
+          <t>Turns</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="78" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>brief.label.energy</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C59" s="78" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="78" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>brief.label.questions</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C60" s="78" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="78" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>brief.label.gaffes</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C61" s="78" t="inlineStr">
+        <is>
+          <t>Gaffes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="78" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>brief.label.guard</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C62" s="78" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="78" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>brief.label.hand</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C63" s="78" t="inlineStr">
+        <is>
+          <t>Your hand</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" s="78" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>brief.label.winning</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C64" s="78" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="78" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>brief.label.decay</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C65" s="78" t="inlineStr">
+        <is>
+          <t>Every turn costs you</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="78" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>brief.turns.none</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C66" s="78" t="inlineStr">
+        <is>
+          <t>no limit. It ends when the questions run out.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="78" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>brief.turns.limit</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C67" s="78" t="inlineStr">
+        <is>
+          <t>{count}. Running out of them is a loss.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E67" s="78" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>brief.energy.pool</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C68" s="78" t="inlineStr">
+        <is>
+          <t>{count} for the whole thing. They do NOT come back at the start of a turn — spend them as a budget.{left}</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>count, left</t>
+        </is>
+      </c>
+      <c r="E68" s="78" t="inlineStr">
+        <is>
+          <t>{left} is "  3 left." during a battle and empty on the briefing screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>brief.energy.left</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C69" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  {count} left.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E69" s="78" t="inlineStr">
+        <is>
+          <t>Appended to the line above once a battle is running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>brief.energy.per_turn</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C70" s="78" t="inlineStr">
+        <is>
+          <t>{count} a turn, back in full when you end the turn.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E70" s="78" t="inlineStr">
+        <is>
+          <t>A playtest could not see WHEN energy came back. That is why this line exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>brief.questions.one_a_turn</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C71" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one a turn, {total} in all. </t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E71" s="78" t="inlineStr">
+        <is>
+          <t>Note the trailing space: the sentence continues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>brief.questions.several</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C72" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{per_turn} a turn, {total} in all. A further card still plays, but nobody is waiting for it. </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>per_turn, total</t>
+        </is>
+      </c>
+      <c r="E72" s="78" t="inlineStr">
+        <is>
+          <t>Trailing space: the sentence continues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>brief.questions.decline</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C73" s="78" t="inlineStr">
+        <is>
+          <t>Leave one unanswered when the turn ends and you have declined it</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="78" t="inlineStr">
+        <is>
+          <t>Joined to whichever ending below applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>brief.questions.ends_stage</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C74" s="78" t="inlineStr">
+        <is>
+          <t>, and here that ends the stage.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="78" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>brief.questions.costs</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C75" s="78" t="inlineStr">
+        <is>
+          <t>, which costs {count} and pleases nobody.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E75" s="78" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>brief.questions.free</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C76" s="78" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="78" t="inlineStr">
+        <is>
+          <t>Where declining costs nothing at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>brief.gaffes.plain</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C77" s="78" t="inlineStr">
+        <is>
+          <t>{count} ends the stage at once.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E77" s="78" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>brief.gaffes.multiplied</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C78" s="78" t="inlineStr">
+        <is>
+          <t>{count} ends the stage at once — and every slip here counts {multiplier} times.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>count, multiplier</t>
+        </is>
+      </c>
+      <c r="E78" s="78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>brief.guard</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C79" s="78" t="inlineStr">
+        <is>
+          <t>it banks up to {count} and carries between turns. Only an attack takes it, and it is spent stopping one.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E79" s="78" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>brief.hand.none</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C80" s="78" t="inlineStr">
+        <is>
+          <t>{count} cards, and you draw no more. Run out and there is nothing left to say.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E80" s="78" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>brief.hand.refill</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C81" s="78" t="inlineStr">
+        <is>
+          <t>drawn back up to {count} at the end of every turn.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E81" s="78" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>brief.winning.score</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C82" s="78" t="inlineStr">
+        <is>
+          <t>there is nothing to reach. However high the support gets by the end is the result, and later stages draw on it.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="78" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>brief.winning.hold</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C83" s="78" t="inlineStr">
+        <is>
+          <t>hold the room until the questions run out.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="78" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>brief.winning.reset</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C84" s="78" t="inlineStr">
+        <is>
+          <t>{count} {unit} wins the argument in front of you. The next one starts again from nothing, gaffes included.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>count, unit</t>
+        </is>
+      </c>
+      <c r="E84" s="78" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>brief.winning.continuous</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C85" s="78" t="inlineStr">
+        <is>
+          <t>{count} {unit} finishes the one in front of you, not the stage. Your record, your hand and the clock carry across all of them.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>count, unit</t>
+        </is>
+      </c>
+      <c r="E85" s="78" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>brief.winning.stream</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C86" s="78" t="inlineStr">
+        <is>
+          <t>{count} {unit} moves the queue along. The clock and your record carry; each new face is fresh energy.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>count, unit</t>
+        </is>
+      </c>
+      <c r="E86" s="78" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>brief.winning.single</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C87" s="78" t="inlineStr">
+        <is>
+          <t>{count} {unit}.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>count, unit</t>
+        </is>
+      </c>
+      <c r="E87" s="78" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>brief.decay</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Details — how this room works</t>
+        </is>
+      </c>
+      <c r="C88" s="78" t="inlineStr">
+        <is>
+          <t>their interest cools by {count}, whatever you say.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E88" s="78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -9272,7 +9272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="43" min="1" max="1"/>
@@ -10629,12 +10629,12 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>brief.heading</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10644,16 +10644,16 @@
           <t>How this room works</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" s="42" t="inlineStr"/>
       <c r="E56" s="78" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="42" t="inlineStr">
         <is>
           <t>brief.bullet</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10663,7 +10663,7 @@
           <t>• {label} — {detail}</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>label, detail</t>
         </is>
@@ -10675,12 +10675,12 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="42" t="inlineStr">
         <is>
           <t>brief.label.turns</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10690,16 +10690,16 @@
           <t>Turns</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" s="42" t="inlineStr"/>
       <c r="E58" s="78" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="42" t="inlineStr">
         <is>
           <t>brief.label.energy</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10709,16 +10709,16 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" s="42" t="inlineStr"/>
       <c r="E59" s="78" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="42" t="inlineStr">
         <is>
           <t>brief.label.questions</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10728,16 +10728,16 @@
           <t>Questions</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" s="42" t="inlineStr"/>
       <c r="E60" s="78" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="42" t="inlineStr">
         <is>
           <t>brief.label.gaffes</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10747,16 +10747,16 @@
           <t>Gaffes</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" s="42" t="inlineStr"/>
       <c r="E61" s="78" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="42" t="inlineStr">
         <is>
           <t>brief.label.guard</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10766,16 +10766,16 @@
           <t>Guard</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" s="42" t="inlineStr"/>
       <c r="E62" s="78" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="42" t="inlineStr">
         <is>
           <t>brief.label.hand</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10785,16 +10785,16 @@
           <t>Your hand</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" s="42" t="inlineStr"/>
       <c r="E63" s="78" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="42" t="inlineStr">
         <is>
           <t>brief.label.winning</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10804,16 +10804,16 @@
           <t>Winning</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" s="42" t="inlineStr"/>
       <c r="E64" s="78" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="42" t="inlineStr">
         <is>
           <t>brief.label.decay</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10823,16 +10823,16 @@
           <t>Every turn costs you</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" s="42" t="inlineStr"/>
       <c r="E65" s="78" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="42" t="inlineStr">
         <is>
           <t>brief.turns.none</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10842,16 +10842,16 @@
           <t>no limit. It ends when the questions run out.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" s="42" t="inlineStr"/>
       <c r="E66" s="78" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="42" t="inlineStr">
         <is>
           <t>brief.turns.limit</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10861,7 +10861,7 @@
           <t>{count}. Running out of them is a loss.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -10869,12 +10869,12 @@
       <c r="E67" s="78" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="42" t="inlineStr">
         <is>
           <t>brief.energy.pool</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10884,7 +10884,7 @@
           <t>{count} for the whole thing. They do NOT come back at the start of a turn — spend them as a budget.{left}</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="42" t="inlineStr">
         <is>
           <t>count, left</t>
         </is>
@@ -10896,12 +10896,12 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="42" t="inlineStr">
         <is>
           <t>brief.energy.left</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10911,7 +10911,7 @@
           <t xml:space="preserve">  {count} left.</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -10923,12 +10923,12 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="42" t="inlineStr">
         <is>
           <t>brief.energy.per_turn</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10938,7 +10938,7 @@
           <t>{count} a turn, back in full when you end the turn.</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -10950,12 +10950,12 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="42" t="inlineStr">
         <is>
           <t>brief.questions.one_a_turn</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10965,7 +10965,7 @@
           <t xml:space="preserve">one a turn, {total} in all. </t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="42" t="inlineStr">
         <is>
           <t>total</t>
         </is>
@@ -10977,12 +10977,12 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="42" t="inlineStr">
         <is>
           <t>brief.questions.several</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -10992,7 +10992,7 @@
           <t xml:space="preserve">{per_turn} a turn, {total} in all. A further card still plays, but nobody is waiting for it. </t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="42" t="inlineStr">
         <is>
           <t>per_turn, total</t>
         </is>
@@ -11004,12 +11004,12 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="42" t="inlineStr">
         <is>
           <t>brief.questions.decline</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11019,7 +11019,7 @@
           <t>Leave one unanswered when the turn ends and you have declined it</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" s="42" t="inlineStr"/>
       <c r="E73" s="78" t="inlineStr">
         <is>
           <t>Joined to whichever ending below applies.</t>
@@ -11027,12 +11027,12 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="42" t="inlineStr">
         <is>
           <t>brief.questions.ends_stage</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11042,16 +11042,16 @@
           <t>, and here that ends the stage.</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" s="42" t="inlineStr"/>
       <c r="E74" s="78" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>brief.questions.costs</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11061,7 +11061,7 @@
           <t>, which costs {count} and pleases nobody.</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11069,12 +11069,12 @@
       <c r="E75" s="78" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="42" t="inlineStr">
         <is>
           <t>brief.questions.free</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11084,7 +11084,7 @@
           <t>.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" s="42" t="inlineStr"/>
       <c r="E76" s="78" t="inlineStr">
         <is>
           <t>Where declining costs nothing at all.</t>
@@ -11092,12 +11092,12 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="42" t="inlineStr">
         <is>
           <t>brief.gaffes.plain</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11107,7 +11107,7 @@
           <t>{count} ends the stage at once.</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11115,12 +11115,12 @@
       <c r="E77" s="78" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="42" t="inlineStr">
         <is>
           <t>brief.gaffes.multiplied</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11130,7 +11130,7 @@
           <t>{count} ends the stage at once — and every slip here counts {multiplier} times.</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="42" t="inlineStr">
         <is>
           <t>count, multiplier</t>
         </is>
@@ -11138,12 +11138,12 @@
       <c r="E78" s="78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="42" t="inlineStr">
         <is>
           <t>brief.guard</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11153,7 +11153,7 @@
           <t>it banks up to {count} and carries between turns. Only an attack takes it, and it is spent stopping one.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11161,12 +11161,12 @@
       <c r="E79" s="78" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="42" t="inlineStr">
         <is>
           <t>brief.hand.none</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11176,7 +11176,7 @@
           <t>{count} cards, and you draw no more. Run out and there is nothing left to say.</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11184,12 +11184,12 @@
       <c r="E80" s="78" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="42" t="inlineStr">
         <is>
           <t>brief.hand.refill</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11199,7 +11199,7 @@
           <t>drawn back up to {count} at the end of every turn.</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -11207,12 +11207,12 @@
       <c r="E81" s="78" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="42" t="inlineStr">
         <is>
           <t>brief.winning.score</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11222,16 +11222,16 @@
           <t>there is nothing to reach. However high the support gets by the end is the result, and later stages draw on it.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" s="42" t="inlineStr"/>
       <c r="E82" s="78" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="42" t="inlineStr">
         <is>
           <t>brief.winning.hold</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11241,16 +11241,16 @@
           <t>hold the room until the questions run out.</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" s="42" t="inlineStr"/>
       <c r="E83" s="78" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="42" t="inlineStr">
         <is>
           <t>brief.winning.reset</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11260,7 +11260,7 @@
           <t>{count} {unit} wins the argument in front of you. The next one starts again from nothing, gaffes included.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="42" t="inlineStr">
         <is>
           <t>count, unit</t>
         </is>
@@ -11268,12 +11268,12 @@
       <c r="E84" s="78" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="42" t="inlineStr">
         <is>
           <t>brief.winning.continuous</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11283,7 +11283,7 @@
           <t>{count} {unit} finishes the one in front of you, not the stage. Your record, your hand and the clock carry across all of them.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="42" t="inlineStr">
         <is>
           <t>count, unit</t>
         </is>
@@ -11291,12 +11291,12 @@
       <c r="E85" s="78" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="42" t="inlineStr">
         <is>
           <t>brief.winning.stream</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11306,7 +11306,7 @@
           <t>{count} {unit} moves the queue along. The clock and your record carry; each new face is fresh energy.</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="42" t="inlineStr">
         <is>
           <t>count, unit</t>
         </is>
@@ -11314,12 +11314,12 @@
       <c r="E86" s="78" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="42" t="inlineStr">
         <is>
           <t>brief.winning.single</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11329,7 +11329,7 @@
           <t>{count} {unit}.</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="42" t="inlineStr">
         <is>
           <t>count, unit</t>
         </is>
@@ -11337,12 +11337,12 @@
       <c r="E87" s="78" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="42" t="inlineStr">
         <is>
           <t>brief.decay</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="42" t="inlineStr">
         <is>
           <t>Details — how this room works</t>
         </is>
@@ -11352,12 +11352,1006 @@
           <t>their interest cools by {count}, whatever you say.</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="42" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
       <c r="E88" s="78" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="42" t="inlineStr">
+        <is>
+          <t>office.title</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C89" s="78" t="inlineStr">
+        <is>
+          <t>The Office</t>
+        </is>
+      </c>
+      <c r="D89" s="42" t="inlineStr"/>
+      <c r="E89" s="78" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="42" t="inlineStr">
+        <is>
+          <t>office.choose_level</t>
+        </is>
+      </c>
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t>Office — buttons</t>
+        </is>
+      </c>
+      <c r="C90" s="78" t="inlineStr">
+        <is>
+          <t>Choose a level</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="inlineStr"/>
+      <c r="E90" s="78" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="42" t="inlineStr">
+        <is>
+          <t>office.management</t>
+        </is>
+      </c>
+      <c r="B91" s="42" t="inlineStr">
+        <is>
+          <t>Office — buttons</t>
+        </is>
+      </c>
+      <c r="C91" s="78" t="inlineStr">
+        <is>
+          <t>Office Management</t>
+        </is>
+      </c>
+      <c r="D91" s="42" t="inlineStr"/>
+      <c r="E91" s="78" t="inlineStr">
+        <is>
+          <t>One door for everything you can spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="42" t="inlineStr">
+        <is>
+          <t>office.organisations</t>
+        </is>
+      </c>
+      <c r="B92" s="42" t="inlineStr">
+        <is>
+          <t>Office — buttons</t>
+        </is>
+      </c>
+      <c r="C92" s="78" t="inlineStr">
+        <is>
+          <t>The organisations</t>
+        </is>
+      </c>
+      <c r="D92" s="42" t="inlineStr"/>
+      <c r="E92" s="78" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="42" t="inlineStr">
+        <is>
+          <t>office.in_order</t>
+        </is>
+      </c>
+      <c r="B93" s="42" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C93" s="78" t="inlineStr">
+        <is>
+          <t>The office is in order.</t>
+        </is>
+      </c>
+      <c r="D93" s="42" t="inlineStr"/>
+      <c r="E93" s="78" t="inlineStr">
+        <is>
+          <t>Shown when your deck is legal and there is nothing to fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_warning</t>
+        </is>
+      </c>
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C94" s="78" t="inlineStr">
+        <is>
+          <t>Your deck: {reason}  —  see Office Management.</t>
+        </is>
+      </c>
+      <c r="D94" s="42" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="E94" s="78" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="42" t="inlineStr">
+        <is>
+          <t>office.report.none</t>
+        </is>
+      </c>
+      <c r="B95" s="42" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C95" s="78" t="inlineStr">
+        <is>
+          <t>Nothing on today. The House sits shortly.</t>
+        </is>
+      </c>
+      <c r="D95" s="42" t="inlineStr"/>
+      <c r="E95" s="78" t="inlineStr">
+        <is>
+          <t>Before your first level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="42" t="inlineStr">
+        <is>
+          <t>office.report.won</t>
+        </is>
+      </c>
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C96" s="78" t="inlineStr">
+        <is>
+          <t>The bill carried. Word has got round.</t>
+        </is>
+      </c>
+      <c r="D96" s="42" t="inlineStr"/>
+      <c r="E96" s="78" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="42" t="inlineStr">
+        <is>
+          <t>office.report.lost</t>
+        </is>
+      </c>
+      <c r="B97" s="42" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C97" s="78" t="inlineStr">
+        <is>
+          <t>The bill failed. There will be questions.</t>
+        </is>
+      </c>
+      <c r="D97" s="42" t="inlineStr"/>
+      <c r="E97" s="78" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="42" t="inlineStr">
+        <is>
+          <t>office.xp</t>
+        </is>
+      </c>
+      <c r="B98" s="42" t="inlineStr">
+        <is>
+          <t>Office — management</t>
+        </is>
+      </c>
+      <c r="C98" s="78" t="inlineStr">
+        <is>
+          <t>XP {count}</t>
+        </is>
+      </c>
+      <c r="D98" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E98" s="78" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="42" t="inlineStr">
+        <is>
+          <t>office.xp_buys</t>
+        </is>
+      </c>
+      <c r="B99" s="42" t="inlineStr">
+        <is>
+          <t>Office — management</t>
+        </is>
+      </c>
+      <c r="C99" s="78" t="inlineStr">
+        <is>
+          <t>Earned by winning stages. Buys new cards.</t>
+        </is>
+      </c>
+      <c r="D99" s="42" t="inlineStr"/>
+      <c r="E99" s="78" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="42" t="inlineStr">
+        <is>
+          <t>office.funds</t>
+        </is>
+      </c>
+      <c r="B100" s="42" t="inlineStr">
+        <is>
+          <t>Office — management</t>
+        </is>
+      </c>
+      <c r="C100" s="78" t="inlineStr">
+        <is>
+          <t>Funds {count}</t>
+        </is>
+      </c>
+      <c r="D100" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E100" s="78" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="42" t="inlineStr">
+        <is>
+          <t>office.funds_buys</t>
+        </is>
+      </c>
+      <c r="B101" s="42" t="inlineStr">
+        <is>
+          <t>Office — management</t>
+        </is>
+      </c>
+      <c r="C101" s="78" t="inlineStr">
+        <is>
+          <t>From donors and backers. Buys the organisations' backing.</t>
+        </is>
+      </c>
+      <c r="D101" s="42" t="inlineStr"/>
+      <c r="E101" s="78" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_count</t>
+        </is>
+      </c>
+      <c r="B102" s="42" t="inlineStr">
+        <is>
+          <t>Office — management</t>
+        </is>
+      </c>
+      <c r="C102" s="78" t="inlineStr">
+        <is>
+          <t>Deck {count} of {size}</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
+        <is>
+          <t>count, size</t>
+        </is>
+      </c>
+      <c r="E102" s="78" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_ready</t>
+        </is>
+      </c>
+      <c r="B103" s="42" t="inlineStr">
+        <is>
+          <t>Office — management</t>
+        </is>
+      </c>
+      <c r="C103" s="78" t="inlineStr">
+        <is>
+          <t>Ready to go in.</t>
+        </is>
+      </c>
+      <c r="D103" s="42" t="inlineStr"/>
+      <c r="E103" s="78" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="42" t="inlineStr">
+        <is>
+          <t>office.new_cards</t>
+        </is>
+      </c>
+      <c r="B104" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C104" s="78" t="inlineStr">
+        <is>
+          <t>New cards</t>
+        </is>
+      </c>
+      <c r="D104" s="42" t="inlineStr"/>
+      <c r="E104" s="78" t="inlineStr">
+        <is>
+          <t>Panel title and button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="42" t="inlineStr">
+        <is>
+          <t>office.your_deck</t>
+        </is>
+      </c>
+      <c r="B105" s="42" t="inlineStr">
+        <is>
+          <t>Office — deck</t>
+        </is>
+      </c>
+      <c r="C105" s="78" t="inlineStr">
+        <is>
+          <t>Your deck</t>
+        </is>
+      </c>
+      <c r="D105" s="42" t="inlineStr"/>
+      <c r="E105" s="78" t="inlineStr">
+        <is>
+          <t>Panel title and button.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="42" t="inlineStr">
+        <is>
+          <t>office.backing</t>
+        </is>
+      </c>
+      <c r="B106" s="42" t="inlineStr">
+        <is>
+          <t>Office — backing</t>
+        </is>
+      </c>
+      <c r="C106" s="78" t="inlineStr">
+        <is>
+          <t>Backing</t>
+        </is>
+      </c>
+      <c r="D106" s="42" t="inlineStr"/>
+      <c r="E106" s="78" t="inlineStr">
+        <is>
+          <t>Button into the backing shop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="42" t="inlineStr">
+        <is>
+          <t>office.cards_blurb</t>
+        </is>
+      </c>
+      <c r="B107" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C107" s="78" t="inlineStr">
+        <is>
+          <t>Cards you unlock join your collection. What you actually take into a debate is chosen on the deck screen.</t>
+        </is>
+      </c>
+      <c r="D107" s="42" t="inlineStr"/>
+      <c r="E107" s="78" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="42" t="inlineStr">
+        <is>
+          <t>office.cards_unlocked.one</t>
+        </is>
+      </c>
+      <c r="B108" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C108" s="78" t="inlineStr">
+        <is>
+          <t>{count} card unlocked so far.</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E108" s="78" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="42" t="inlineStr">
+        <is>
+          <t>office.cards_unlocked.other</t>
+        </is>
+      </c>
+      <c r="B109" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C109" s="78" t="inlineStr">
+        <is>
+          <t>{count} cards unlocked so far.</t>
+        </is>
+      </c>
+      <c r="D109" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E109" s="78" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="42" t="inlineStr">
+        <is>
+          <t>office.unlock</t>
+        </is>
+      </c>
+      <c r="B110" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C110" s="78" t="inlineStr">
+        <is>
+          <t>Unlock</t>
+        </is>
+      </c>
+      <c r="D110" s="42" t="inlineStr"/>
+      <c r="E110" s="78" t="inlineStr">
+        <is>
+          <t>The button on a card you can afford.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="42" t="inlineStr">
+        <is>
+          <t>office.card_line</t>
+        </is>
+      </c>
+      <c r="B111" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C111" s="78" t="inlineStr">
+        <is>
+          <t>{suit} · {effect}</t>
+        </is>
+      </c>
+      <c r="D111" s="42" t="inlineStr">
+        <is>
+          <t>suit, effect</t>
+        </is>
+      </c>
+      <c r="E111" s="78" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_chosen</t>
+        </is>
+      </c>
+      <c r="B112" s="42" t="inlineStr">
+        <is>
+          <t>Office — deck</t>
+        </is>
+      </c>
+      <c r="C112" s="78" t="inlineStr">
+        <is>
+          <t>{count} of {size} chosen{warning}</t>
+        </is>
+      </c>
+      <c r="D112" s="42" t="inlineStr">
+        <is>
+          <t>count, size, warning</t>
+        </is>
+      </c>
+      <c r="E112" s="78" t="inlineStr">
+        <is>
+          <t>{warning} is empty when the deck is legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_warning_suffix</t>
+        </is>
+      </c>
+      <c r="B113" s="42" t="inlineStr">
+        <is>
+          <t>Office — deck</t>
+        </is>
+      </c>
+      <c r="C113" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  —  {reason}</t>
+        </is>
+      </c>
+      <c r="D113" s="42" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="E113" s="78" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_tap</t>
+        </is>
+      </c>
+      <c r="B114" s="42" t="inlineStr">
+        <is>
+          <t>Office — deck</t>
+        </is>
+      </c>
+      <c r="C114" s="78" t="inlineStr">
+        <is>
+          <t>Tap a card to take it in or leave it out.</t>
+        </is>
+      </c>
+      <c r="D114" s="42" t="inlineStr"/>
+      <c r="E114" s="78" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="42" t="inlineStr">
+        <is>
+          <t>office.deck_confirm</t>
+        </is>
+      </c>
+      <c r="B115" s="42" t="inlineStr">
+        <is>
+          <t>Office — deck</t>
+        </is>
+      </c>
+      <c r="C115" s="78" t="inlineStr">
+        <is>
+          <t>Take these in</t>
+        </is>
+      </c>
+      <c r="D115" s="42" t="inlineStr"/>
+      <c r="E115" s="78" t="inlineStr">
+        <is>
+          <t>Only offered when the deck is legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="42" t="inlineStr">
+        <is>
+          <t>office.orgs_blurb</t>
+        </is>
+      </c>
+      <c r="B116" s="42" t="inlineStr">
+        <is>
+          <t>Office — organisations</t>
+        </is>
+      </c>
+      <c r="C116" s="78" t="inlineStr">
+        <is>
+          <t>Answering a reporter in the suit their question invites pleases the organisation behind it, and that standing is carried between levels.</t>
+        </is>
+      </c>
+      <c r="D116" s="42" t="inlineStr"/>
+      <c r="E116" s="78" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="42" t="inlineStr">
+        <is>
+          <t>office.backing_blurb</t>
+        </is>
+      </c>
+      <c r="B117" s="42" t="inlineStr">
+        <is>
+          <t>Office — backing</t>
+        </is>
+      </c>
+      <c r="C117" s="78" t="inlineStr">
+        <is>
+          <t>An organisation backs you once your standing with it is high enough. Answering a reporter in the suit their question invites is what raises it.</t>
+        </is>
+      </c>
+      <c r="D117" s="42" t="inlineStr"/>
+      <c r="E117" s="78" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="42" t="inlineStr">
+        <is>
+          <t>office.nothing_for_sale</t>
+        </is>
+      </c>
+      <c r="B118" s="42" t="inlineStr">
+        <is>
+          <t>Office — backing</t>
+        </is>
+      </c>
+      <c r="C118" s="78" t="inlineStr">
+        <is>
+          <t>Nothing is for sale.</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr"/>
+      <c r="E118" s="78" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="42" t="inlineStr">
+        <is>
+          <t>office.take_backing</t>
+        </is>
+      </c>
+      <c r="B119" s="42" t="inlineStr">
+        <is>
+          <t>Office — backing</t>
+        </is>
+      </c>
+      <c r="C119" s="78" t="inlineStr">
+        <is>
+          <t>Take their backing</t>
+        </is>
+      </c>
+      <c r="D119" s="42" t="inlineStr"/>
+      <c r="E119" s="78" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="42" t="inlineStr">
+        <is>
+          <t>office.no_effect_yet</t>
+        </is>
+      </c>
+      <c r="B120" s="42" t="inlineStr">
+        <is>
+          <t>Office — backing</t>
+        </is>
+      </c>
+      <c r="C120" s="78" t="inlineStr">
+        <is>
+          <t>No effect yet — your record always opens clean, so there is nothing here to take off.</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr"/>
+      <c r="E120" s="78" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="42" t="inlineStr">
+        <is>
+          <t>office.not_active_yet</t>
+        </is>
+      </c>
+      <c r="B121" s="42" t="inlineStr">
+        <is>
+          <t>Office — backing</t>
+        </is>
+      </c>
+      <c r="C121" s="78" t="inlineStr">
+        <is>
+          <t>Not active yet — this effect is still to be built.</t>
+        </is>
+      </c>
+      <c r="D121" s="42" t="inlineStr"/>
+      <c r="E121" s="78" t="inlineStr">
+        <is>
+          <t>Six of the fifteen organisations' effects need machinery that is not built.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="42" t="inlineStr">
+        <is>
+          <t>shop.card_no_id</t>
+        </is>
+      </c>
+      <c r="B122" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C122" s="78" t="inlineStr">
+        <is>
+          <t>This card has no ID.</t>
+        </is>
+      </c>
+      <c r="D122" s="42" t="inlineStr"/>
+      <c r="E122" s="78" t="inlineStr">
+        <is>
+          <t>Should never be seen; it means the data is broken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="42" t="inlineStr">
+        <is>
+          <t>shop.already_yours</t>
+        </is>
+      </c>
+      <c r="B123" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C123" s="78" t="inlineStr">
+        <is>
+          <t>Already yours.</t>
+        </is>
+      </c>
+      <c r="D123" s="42" t="inlineStr"/>
+      <c r="E123" s="78" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="42" t="inlineStr">
+        <is>
+          <t>shop.xp_short</t>
+        </is>
+      </c>
+      <c r="B124" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C124" s="78" t="inlineStr">
+        <is>
+          <t>{count} XP short.</t>
+        </is>
+      </c>
+      <c r="D124" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E124" s="78" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="42" t="inlineStr">
+        <is>
+          <t>shop.mod_no_id</t>
+        </is>
+      </c>
+      <c r="B125" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C125" s="78" t="inlineStr">
+        <is>
+          <t>This modifier has no ID.</t>
+        </is>
+      </c>
+      <c r="D125" s="42" t="inlineStr"/>
+      <c r="E125" s="78" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="42" t="inlineStr">
+        <is>
+          <t>shop.not_for_sale</t>
+        </is>
+      </c>
+      <c r="B126" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C126" s="78" t="inlineStr">
+        <is>
+          <t>Not for sale.</t>
+        </is>
+      </c>
+      <c r="D126" s="42" t="inlineStr"/>
+      <c r="E126" s="78" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="42" t="inlineStr">
+        <is>
+          <t>shop.standing_needed</t>
+        </is>
+      </c>
+      <c r="B127" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C127" s="78" t="inlineStr">
+        <is>
+          <t>Standing {have} of {needed} needed.</t>
+        </is>
+      </c>
+      <c r="D127" s="42" t="inlineStr">
+        <is>
+          <t>have, needed</t>
+        </is>
+      </c>
+      <c r="E127" s="78" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="42" t="inlineStr">
+        <is>
+          <t>shop.funds_short</t>
+        </is>
+      </c>
+      <c r="B128" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C128" s="78" t="inlineStr">
+        <is>
+          <t>{count} short.</t>
+        </is>
+      </c>
+      <c r="D128" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E128" s="78" t="inlineStr">
+        <is>
+          <t>Funds, not XP — the sentence sits under a Funds heading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="42" t="inlineStr">
+        <is>
+          <t>shop.not_yours</t>
+        </is>
+      </c>
+      <c r="B129" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C129" s="78" t="inlineStr">
+        <is>
+          <t>{card} is not yours.</t>
+        </is>
+      </c>
+      <c r="D129" s="42" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="E129" s="78" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="42" t="inlineStr">
+        <is>
+          <t>shop.in_twice</t>
+        </is>
+      </c>
+      <c r="B130" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C130" s="78" t="inlineStr">
+        <is>
+          <t>{card} is in twice.</t>
+        </is>
+      </c>
+      <c r="D130" s="42" t="inlineStr">
+        <is>
+          <t>card</t>
+        </is>
+      </c>
+      <c r="E130" s="78" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="42" t="inlineStr">
+        <is>
+          <t>shop.more_to_choose</t>
+        </is>
+      </c>
+      <c r="B131" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C131" s="78" t="inlineStr">
+        <is>
+          <t>{count} more to choose.</t>
+        </is>
+      </c>
+      <c r="D131" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E131" s="78" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="42" t="inlineStr">
+        <is>
+          <t>shop.too_many</t>
+        </is>
+      </c>
+      <c r="B132" s="42" t="inlineStr">
+        <is>
+          <t>Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C132" s="78" t="inlineStr">
+        <is>
+          <t>{count} too many.</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E132" s="78" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="42" t="inlineStr">
+        <is>
+          <t>office.card_title</t>
+        </is>
+      </c>
+      <c r="B133" s="42" t="inlineStr">
+        <is>
+          <t>Office — cards</t>
+        </is>
+      </c>
+      <c r="C133" s="78" t="inlineStr">
+        <is>
+          <t>{name} {name_jp}  —  {cost} XP</t>
+        </is>
+      </c>
+      <c r="D133" s="42" t="inlineStr">
+        <is>
+          <t>name, name_jp, cost</t>
+        </is>
+      </c>
+      <c r="E133" s="42" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>office.where_you_stand</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C134" s="78" t="inlineStr">
+        <is>
+          <t>Where you stand</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Heading above your four standings. Browser build only so far; the Godot Office shows them without a heading.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -9272,7 +9272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="43" min="1" max="1"/>
@@ -12328,15 +12328,15 @@
           <t>name, name_jp, cost</t>
         </is>
       </c>
-      <c r="E133" s="42" t="inlineStr"/>
+      <c r="E133" s="78" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="42" t="inlineStr">
         <is>
           <t>office.where_you_stand</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="42" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
@@ -12346,12 +12346,1553 @@
           <t>Where you stand</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
+      <c r="D134" s="42" t="inlineStr"/>
+      <c r="E134" s="78" t="inlineStr">
         <is>
           <t>Heading above your four standings. Browser build only so far; the Godot Office shows them without a heading.</t>
         </is>
       </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.walked_away</t>
+        </is>
+      </c>
+      <c r="B135" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C135" s="78" t="inlineStr">
+        <is>
+          <t>You walked away from the question. That is the story now.</t>
+        </is>
+      </c>
+      <c r="D135" s="42" t="inlineStr"/>
+      <c r="E135" s="78" t="inlineStr">
+        <is>
+          <t>Declining a question in a room where that ends it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.gaffe_limit</t>
+        </is>
+      </c>
+      <c r="B136" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C136" s="78" t="inlineStr">
+        <is>
+          <t>The gaffe meter filled.</t>
+        </is>
+      </c>
+      <c r="D136" s="42" t="inlineStr"/>
+      <c r="E136" s="78" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.committee_for</t>
+        </is>
+      </c>
+      <c r="B137" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C137" s="78" t="inlineStr">
+        <is>
+          <t>A majority of the committee locked in favour.</t>
+        </is>
+      </c>
+      <c r="D137" s="42" t="inlineStr"/>
+      <c r="E137" s="78" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.committee_against</t>
+        </is>
+      </c>
+      <c r="B138" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C138" s="78" t="inlineStr">
+        <is>
+          <t>Too many members locked against — a majority is no longer possible.</t>
+        </is>
+      </c>
+      <c r="D138" s="42" t="inlineStr"/>
+      <c r="E138" s="78" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.all_argued_out</t>
+        </is>
+      </c>
+      <c r="B139" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C139" s="78" t="inlineStr">
+        <is>
+          <t>Every opponent has been argued out of the chamber.</t>
+        </is>
+      </c>
+      <c r="D139" s="42" t="inlineStr"/>
+      <c r="E139" s="78" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.opponent_first</t>
+        </is>
+      </c>
+      <c r="B140" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C140" s="78" t="inlineStr">
+        <is>
+          <t>The opponent reached the threshold first.</t>
+        </is>
+      </c>
+      <c r="D140" s="42" t="inlineStr"/>
+      <c r="E140" s="78" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.fell_below</t>
+        </is>
+      </c>
+      <c r="B141" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C141" s="78" t="inlineStr">
+        <is>
+          <t>Support fell below the line during the debate.</t>
+        </is>
+      </c>
+      <c r="D141" s="42" t="inlineStr"/>
+      <c r="E141" s="78" t="inlineStr">
+        <is>
+          <t>A TV debate, where you must stay above the line every turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.survived</t>
+        </is>
+      </c>
+      <c r="B142" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C142" s="78" t="inlineStr">
+        <is>
+          <t>Survived the whole debate above the line.</t>
+        </is>
+      </c>
+      <c r="D142" s="42" t="inlineStr"/>
+      <c r="E142" s="78" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.all_argued_down</t>
+        </is>
+      </c>
+      <c r="B143" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C143" s="78" t="inlineStr">
+        <is>
+          <t>All {count} were argued down.</t>
+        </is>
+      </c>
+      <c r="D143" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E143" s="78" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.threshold</t>
+        </is>
+      </c>
+      <c r="B144" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C144" s="78" t="inlineStr">
+        <is>
+          <t>The support threshold was reached.</t>
+        </is>
+      </c>
+      <c r="D144" s="42" t="inlineStr"/>
+      <c r="E144" s="78" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.closed_on</t>
+        </is>
+      </c>
+      <c r="B145" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C145" s="78" t="inlineStr">
+        <is>
+          <t>{stage} closed on {closing}.</t>
+        </is>
+      </c>
+      <c r="D145" s="42" t="inlineStr">
+        <is>
+          <t>stage, closing</t>
+        </is>
+      </c>
+      <c r="E145" s="78" t="inlineStr">
+        <is>
+          <t>{closing} is "46% of the room" or "46 support".</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.closed_on_unnamed</t>
+        </is>
+      </c>
+      <c r="B146" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C146" s="78" t="inlineStr">
+        <is>
+          <t>It closed on {closing}.</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>closing</t>
+        </is>
+      </c>
+      <c r="E146" s="78" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.percent_of_room</t>
+        </is>
+      </c>
+      <c r="B147" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C147" s="78" t="inlineStr">
+        <is>
+          <t>{count}% of the room</t>
+        </is>
+      </c>
+      <c r="D147" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E147" s="78" t="inlineStr">
+        <is>
+          <t>Slots into the line above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.amount_of_unit</t>
+        </is>
+      </c>
+      <c r="B148" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C148" s="78" t="inlineStr">
+        <is>
+          <t>{count} {unit}</t>
+        </is>
+      </c>
+      <c r="D148" s="42" t="inlineStr">
+        <is>
+          <t>count, unit</t>
+        </is>
+      </c>
+      <c r="E148" s="78" t="inlineStr">
+        <is>
+          <t>Slots into the line above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.time_ahead</t>
+        </is>
+      </c>
+      <c r="B149" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C149" s="78" t="inlineStr">
+        <is>
+          <t>Time ran out with the player ahead.</t>
+        </is>
+      </c>
+      <c r="D149" s="42" t="inlineStr"/>
+      <c r="E149" s="78" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.time_behind</t>
+        </is>
+      </c>
+      <c r="B150" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C150" s="78" t="inlineStr">
+        <is>
+          <t>Time ran out with the player behind.</t>
+        </is>
+      </c>
+      <c r="D150" s="42" t="inlineStr"/>
+      <c r="E150" s="78" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.time_no_decision</t>
+        </is>
+      </c>
+      <c r="B151" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C151" s="78" t="inlineStr">
+        <is>
+          <t>Time ran out with no decision. The stage restarts.</t>
+        </is>
+      </c>
+      <c r="D151" s="42" t="inlineStr"/>
+      <c r="E151" s="78" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.time_short</t>
+        </is>
+      </c>
+      <c r="B152" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C152" s="78" t="inlineStr">
+        <is>
+          <t>Time ran out before the threshold was reached.</t>
+        </is>
+      </c>
+      <c r="D152" s="42" t="inlineStr"/>
+      <c r="E152" s="78" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.concludes</t>
+        </is>
+      </c>
+      <c r="B153" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C153" s="78" t="inlineStr">
+        <is>
+          <t>{stage} concludes.</t>
+        </is>
+      </c>
+      <c r="D153" s="42" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="E153" s="78" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.concludes_unnamed</t>
+        </is>
+      </c>
+      <c r="B154" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C154" s="78" t="inlineStr">
+        <is>
+          <t>It concludes.</t>
+        </is>
+      </c>
+      <c r="D154" s="42" t="inlineStr"/>
+      <c r="E154" s="78" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.nothing_left</t>
+        </is>
+      </c>
+      <c r="B155" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C155" s="78" t="inlineStr">
+        <is>
+          <t>The questions ran on, but there was nothing left to say.</t>
+        </is>
+      </c>
+      <c r="D155" s="42" t="inlineStr"/>
+      <c r="E155" s="78" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.unanswered.one</t>
+        </is>
+      </c>
+      <c r="B156" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C156" s="78" t="inlineStr">
+        <is>
+          <t>One question went unanswered.</t>
+        </is>
+      </c>
+      <c r="D156" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E156" s="78" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="42" t="inlineStr">
+        <is>
+          <t>outcome.reason.unanswered.other</t>
+        </is>
+      </c>
+      <c r="B157" s="42" t="inlineStr">
+        <is>
+          <t>End of stage — why</t>
+        </is>
+      </c>
+      <c r="C157" s="78" t="inlineStr">
+        <is>
+          <t>{count} questions went unanswered.</t>
+        </is>
+      </c>
+      <c r="D157" s="42" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E157" s="78" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="42" t="inlineStr">
+        <is>
+          <t>caption.turn</t>
+        </is>
+      </c>
+      <c r="B158" s="42" t="inlineStr">
+        <is>
+          <t>Battle — header</t>
+        </is>
+      </c>
+      <c r="C158" s="78" t="inlineStr">
+        <is>
+          <t>Turn {turn} of {total}</t>
+        </is>
+      </c>
+      <c r="D158" s="42" t="inlineStr">
+        <is>
+          <t>turn, total</t>
+        </is>
+      </c>
+      <c r="E158" s="78" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="42" t="inlineStr">
+        <is>
+          <t>caption.question</t>
+        </is>
+      </c>
+      <c r="B159" s="42" t="inlineStr">
+        <is>
+          <t>Battle — header</t>
+        </is>
+      </c>
+      <c r="C159" s="78" t="inlineStr">
+        <is>
+          <t>Question {number} of {total}</t>
+        </is>
+      </c>
+      <c r="D159" s="42" t="inlineStr">
+        <is>
+          <t>number, total</t>
+        </is>
+      </c>
+      <c r="E159" s="78" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="42" t="inlineStr">
+        <is>
+          <t>caption.opponent</t>
+        </is>
+      </c>
+      <c r="B160" s="42" t="inlineStr">
+        <is>
+          <t>Battle — header</t>
+        </is>
+      </c>
+      <c r="C160" s="78" t="inlineStr">
+        <is>
+          <t>{number} of {total}</t>
+        </is>
+      </c>
+      <c r="D160" s="42" t="inlineStr">
+        <is>
+          <t>number, total</t>
+        </is>
+      </c>
+      <c r="E160" s="78" t="inlineStr">
+        <is>
+          <t>Beside the opponent's name in a room with several.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="42" t="inlineStr">
+        <is>
+          <t>caption.stage</t>
+        </is>
+      </c>
+      <c r="B161" s="42" t="inlineStr">
+        <is>
+          <t>Briefing</t>
+        </is>
+      </c>
+      <c r="C161" s="78" t="inlineStr">
+        <is>
+          <t>Stage {number} of {total}</t>
+        </is>
+      </c>
+      <c r="D161" s="42" t="inlineStr">
+        <is>
+          <t>number, total</t>
+        </is>
+      </c>
+      <c r="E161" s="78" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="42" t="inlineStr">
+        <is>
+          <t>intent.waiting</t>
+        </is>
+      </c>
+      <c r="B162" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their intent</t>
+        </is>
+      </c>
+      <c r="C162" s="78" t="inlineStr">
+        <is>
+          <t>Waiting</t>
+        </is>
+      </c>
+      <c r="D162" s="42" t="inlineStr"/>
+      <c r="E162" s="78" t="inlineStr">
+        <is>
+          <t>They have no move, or none worth making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="42" t="inlineStr">
+        <is>
+          <t>intent.attacking</t>
+        </is>
+      </c>
+      <c r="B163" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their intent</t>
+        </is>
+      </c>
+      <c r="C163" s="78" t="inlineStr">
+        <is>
+          <t>Attacking · {amount}</t>
+        </is>
+      </c>
+      <c r="D163" s="42" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E163" s="78" t="inlineStr">
+        <is>
+          <t>{amount} is "−6" or "−1 to −6".</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="42" t="inlineStr">
+        <is>
+          <t>intent.gaining</t>
+        </is>
+      </c>
+      <c r="B164" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their intent</t>
+        </is>
+      </c>
+      <c r="C164" s="78" t="inlineStr">
+        <is>
+          <t>Gaining · {amount}</t>
+        </is>
+      </c>
+      <c r="D164" s="42" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E164" s="78" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="42" t="inlineStr">
+        <is>
+          <t>intent.guarding</t>
+        </is>
+      </c>
+      <c r="B165" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their intent</t>
+        </is>
+      </c>
+      <c r="C165" s="78" t="inlineStr">
+        <is>
+          <t>Guarding · {amount}</t>
+        </is>
+      </c>
+      <c r="D165" s="42" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E165" s="78" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="42" t="inlineStr">
+        <is>
+          <t>intent.pressuring</t>
+        </is>
+      </c>
+      <c r="B166" s="42" t="inlineStr">
+        <is>
+          <t>Battle — their intent</t>
+        </is>
+      </c>
+      <c r="C166" s="78" t="inlineStr">
+        <is>
+          <t>Pressuring · {amount}</t>
+        </is>
+      </c>
+      <c r="D166" s="42" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E166" s="78" t="inlineStr">
+        <is>
+          <t>A committee chair leaning on a member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>intent.range</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Battle · opponent intent</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>{low} to {high}</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>low, high</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Joins the two ends of a move that could be anything in a range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>carried.went_well</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Battle · details panel</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>{name} went well: you start {count} ahead.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>name, count</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>carried.went_badly</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Battle · details panel</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>{name} went badly: you start {count} behind.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>name, count</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>carried.pleased</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Battle · details panel</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Pleased at the press conference: {names}.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>names</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>carried.nothing</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Battle · details panel</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Nothing carried over from the earlier stages.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Shown when nothing carried. Reword freely — the screen no longer reads this sentence to decide anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>reward.by_finish</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Office · level briefing</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>{name}, by how far above {baseline} you finish (1 per {per})</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>name, baseline, per</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>{name} is one of the four standing names — see the warning on those rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>reward.head_start</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Office · level briefing</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>A head start later in the level, 1 per {per} above {baseline}</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>per, baseline</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>reward.standing</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Office · level briefing</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Standing with whichever organisations your answers please</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>reward.delta</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Office · level briefing</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>{name} {amount}</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>name, amount</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>{amount} already carries its + or −.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>reward.nothing_set</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Office · level briefing</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Nothing in this level pays out yet. The slots are in the data waiting for numbers, and the moment they have any, they will land here and on your standing.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>modifier.player_start_support</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Office · backing shop</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Start {count} ahead.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>modifier.starting_gaffe</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Office · backing shop</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Start with {count} less on the gaffe meter.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>modifier.kaban_per_stage_win</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Office · backing shop</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>+{count} funds for every stage won.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>battle.one_at_a_time</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Battle · details panel</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>{count} of them, one at a time. You are on {number}.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>count, number</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>battle.default_pattern</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Battle · details panel</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>This opponent has no move pattern of their own yet, so they are using the shared default from rules.json and playing generically.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>battle.last_question</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Battle · press conference</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>That was the last question.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>battle.who_and_caption</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Battle · speaker row</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>{who}  ·  {caption}</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>who, caption</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>battle.your_guard</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Battle · status row</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Guard {count} / {cap}</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>count, cap</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>battle.their_guard</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Battle · status row</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>They guard {count} / {cap}</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>count, cap</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>bar.to_win</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>{amount} to win</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>bar.to_advance</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>{amount} to advance</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Shown on the floor, where the threshold ends one debater rather than the stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>bar.take_the_room</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Take as much of the room as you can</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>bar.raise_as_high</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Raise {unit} as high as you can</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>bar.one_sided</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>{unit} {count} of {total}</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>unit, count, total</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>bar.two_sided</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>You {you} · Undecided {undecided} · {them} {theirs}</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>you, undecided, them, theirs</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>bar.them</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Battle · support bar</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Them</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Stands in for an opponent with no name, or one too long for the row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>card.gain</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Gain {count}.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>card.opponent</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Opponent −{count}.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>card.guard</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Guard {count}.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>card.draw</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Draw {count}.</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>card.gaffe</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Gaffe {amount}.</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>{amount} already carries its + or −.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>card.does_nothing</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Nothing this card does counts in this room.</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>card.answers_question</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Card · effect line</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Answers this question.</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>card.line</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Card · opened card</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>{suit} · {type} · costs {cost}</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>suit, type, cost</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>card.in_this_room</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Card · opened card</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>In this room: {effect}</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>effect</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -40361,7 +40361,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AH46"/>
+  <dimension ref="A1:AO46"/>
   <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.01171875" customWidth="1"/>
@@ -40387,7 +40387,7 @@
     <col min="29" max="29" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>150</v>
       </c>
@@ -40490,8 +40490,43 @@
       <c r="AH1" s="69" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bar Model</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy Mode</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy Pool</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sequence Mode</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opponent Count</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question Pool</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reputation Affects Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>183</v>
       </c>
@@ -40597,8 +40632,33 @@
       <c r="AH2" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>190</v>
       </c>
@@ -40704,8 +40764,33 @@
       <c r="AH3" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:41" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>195</v>
       </c>
@@ -40811,8 +40896,33 @@
       <c r="AH4" s="82">
         <v>-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>201</v>
       </c>
@@ -40918,8 +41028,38 @@
       <c r="AH5" s="82">
         <v>-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AN5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">press_conference</t>
+        </is>
+      </c>
+      <c r="AO5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>206</v>
       </c>
@@ -41025,8 +41165,33 @@
       <c r="AH6" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>211</v>
       </c>
@@ -41132,8 +41297,33 @@
       <c r="AH7" s="82">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Survival</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>215</v>
       </c>
@@ -41239,8 +41429,33 @@
       <c r="AH8" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:41" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>221</v>
       </c>
@@ -41346,8 +41561,33 @@
       <c r="AH9" s="81">
         <v>-5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>225</v>
       </c>
@@ -41453,8 +41693,33 @@
       <c r="AH10" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>230</v>
       </c>
@@ -41560,8 +41825,33 @@
       <c r="AH11" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>234</v>
       </c>
@@ -41667,8 +41957,33 @@
       <c r="AH12" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>238</v>
       </c>
@@ -41774,8 +42089,33 @@
       <c r="AH13" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>242</v>
       </c>
@@ -41881,8 +42221,33 @@
       <c r="AH14" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>246</v>
       </c>
@@ -41988,8 +42353,33 @@
       <c r="AH15" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:41" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>250</v>
       </c>
@@ -42095,8 +42485,33 @@
       <c r="AH16" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>254</v>
       </c>
@@ -42202,8 +42617,33 @@
       <c r="AH17" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>258</v>
       </c>
@@ -42309,8 +42749,33 @@
       <c r="AH18" s="82">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>262</v>
       </c>
@@ -42416,8 +42881,33 @@
       <c r="AH19" s="4">
         <v>-10</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Committee</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>267</v>
       </c>
@@ -42523,8 +43013,38 @@
       <c r="AH20" s="4">
         <v>-5</v>
       </c>
-    </row>
-    <row r="21" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AN20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">media_ambush</t>
+        </is>
+      </c>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>271</v>
       </c>
@@ -42630,8 +43150,38 @@
       <c r="AH21" s="4">
         <v>-1</v>
       </c>
-    </row>
-    <row r="22" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AN21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lobbyist_meeting</t>
+        </is>
+      </c>
+      <c r="AO21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>275</v>
       </c>
@@ -42736,6 +43286,36 @@
       </c>
       <c r="AH22" s="4">
         <v>0</v>
+      </c>
+      <c r="AI22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shared_pool</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">per_turn</t>
+        </is>
+      </c>
+      <c r="AL22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">single</t>
+        </is>
+      </c>
+      <c r="AM22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="AN22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">policy_study</t>
+        </is>
+      </c>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.2">

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -40361,7 +40361,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AO46"/>
+  <dimension ref="A1:AP46"/>
   <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.01171875" customWidth="1"/>
@@ -40387,7 +40387,7 @@
     <col min="29" max="29" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>150</v>
       </c>
@@ -40525,6 +40525,11 @@
           <t xml:space="preserve">Reputation Affects Start</t>
         </is>
       </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reveal In Briefing</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:41" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
@@ -42907,7 +42912,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>267</v>
       </c>
@@ -43039,6 +43044,11 @@
         </is>
       </c>
       <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="AP20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -36,6 +36,8 @@
     <sheet name="Study Session Questions" sheetId="20" r:id="rId21"/>
     <sheet name="Media Ambush Questions" sheetId="21" r:id="rId22"/>
     <sheet name="Question Themes" sheetId="22" r:id="rId23"/>
+    <sheet name="Visitors" sheetId="24" r:id="rId28"/>
+    <sheet name="Visitor Questions" sheetId="25" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Cards!$A$1:$S$55</definedName>
@@ -40221,6 +40223,229 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visitor ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visitor (EN)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visitor (JP)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romaji</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Role</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reward</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample Constituent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sampuru</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Constituent</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ST07</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BO01 +1; BO02 +1-3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BO01 -1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visitor ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Question text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choice A</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choice B</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choice C</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choice D</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct Choice</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Response - Right</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Response - Wrong</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reaction - Right</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reaction - Wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VQ01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VI01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What does the district need most right now?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More funding for schools</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lower local taxes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing, everything is fine</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A new stadium</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exactly what I've been saying!</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hm, I'm not sure that's right.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nods approvingly.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frowns, unconvinced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -10342,7 +10342,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DBCFC6-E562-474C-8005-C80E8AAC1DE0}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.84765625" customWidth="1"/>
@@ -10351,7 +10351,7 @@
     <col min="7" max="7" width="20.04296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A1" s="106" t="s">
         <v>2553</v>
       </c>
@@ -10373,8 +10373,13 @@
       <c r="G1" s="106" t="s">
         <v>2557</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.2">
+      <c r="H1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="108" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>2566</v>
       </c>
@@ -10397,7 +10402,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="108" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>2571</v>
       </c>
@@ -10420,7 +10425,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="94.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A4" s="107" t="s">
         <v>2576</v>
       </c>
@@ -10443,7 +10448,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A5" s="107" t="s">
         <v>2581</v>
       </c>
@@ -10466,7 +10471,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A6" s="107" t="s">
         <v>2584</v>
       </c>
@@ -10489,7 +10494,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A7" s="107" t="s">
         <v>2587</v>
       </c>
@@ -10512,7 +10517,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="107" t="s">
         <v>2590</v>
       </c>
@@ -10535,7 +10540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A9" s="107" t="s">
         <v>2593</v>
       </c>
@@ -10558,7 +10563,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A10" s="107" t="s">
         <v>2596</v>
       </c>
@@ -10581,7 +10586,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A11" s="107" t="s">
         <v>2599</v>
       </c>
@@ -10604,7 +10609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A12" s="107" t="s">
         <v>2601</v>
       </c>
@@ -10627,7 +10632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A13" s="107" t="s">
         <v>2604</v>
       </c>
@@ -10650,7 +10655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="107" t="s">
         <v>2606</v>
       </c>
@@ -10673,7 +10678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A15" s="107" t="s">
         <v>2608</v>
       </c>
@@ -10696,7 +10701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A16" s="107" t="s">
         <v>2611</v>
       </c>
@@ -10719,7 +10724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="107" t="s">
         <v>2614</v>
       </c>
@@ -10742,7 +10747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A18" s="107" t="s">
         <v>2617</v>
       </c>
@@ -10765,7 +10770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A19" s="107" t="s">
         <v>2620</v>
       </c>
@@ -10788,7 +10793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="107" t="s">
         <v>2623</v>
       </c>
@@ -10811,7 +10816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A21" s="107" t="s">
         <v>2626</v>
       </c>
@@ -10834,7 +10839,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="107" t="s">
         <v>2630</v>
       </c>
@@ -10857,7 +10862,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="107" t="s">
         <v>2634</v>
       </c>
@@ -10880,7 +10885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A24" s="107" t="s">
         <v>2638</v>
       </c>
@@ -10903,7 +10908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A25" s="107" t="s">
         <v>2642</v>
       </c>
@@ -10926,7 +10931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="107" t="s">
         <v>2646</v>
       </c>
@@ -10949,7 +10954,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A27" s="107" t="s">
         <v>2650</v>
       </c>
@@ -10972,7 +10977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A28" s="107" t="s">
         <v>2757</v>
       </c>
@@ -10995,7 +11000,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A29" s="107" t="s">
         <v>2758</v>
       </c>
@@ -11018,7 +11023,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A30" s="107" t="s">
         <v>2759</v>
       </c>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -10342,7 +10342,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DBCFC6-E562-474C-8005-C80E8AAC1DE0}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.84765625" customWidth="1"/>
@@ -10351,7 +10351,7 @@
     <col min="7" max="7" width="20.04296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A1" s="106" t="s">
         <v>2553</v>
       </c>
@@ -10378,8 +10378,43 @@
           <t xml:space="preserve">Grants</t>
         </is>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="108" x14ac:dyDescent="0.2">
+      <c r="I1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Icon</t>
+        </is>
+      </c>
+      <c r="J1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use In Office</t>
+        </is>
+      </c>
+      <c r="K1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use In Stage</t>
+        </is>
+      </c>
+      <c r="L1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duration</t>
+        </is>
+      </c>
+      <c r="M1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uses Per Turn</t>
+        </is>
+      </c>
+      <c r="N1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stack Cap</t>
+        </is>
+      </c>
+      <c r="O1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Purchase Limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="108" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>2566</v>
       </c>
@@ -10401,8 +10436,31 @@
       <c r="G2" s="107" t="s">
         <v>2570</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="108" x14ac:dyDescent="0.2">
+      <c r="H2" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BO01|BO02 +1</t>
+        </is>
+      </c>
+      <c r="I2" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">policy_research</t>
+        </is>
+      </c>
+      <c r="J2" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K2" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="O2" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="108" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>2571</v>
       </c>
@@ -10424,8 +10482,31 @@
       <c r="G3" s="107" t="s">
         <v>2575</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="94.5" x14ac:dyDescent="0.2">
+      <c r="H3" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BO05|BO08|BO09|BO10|BO13|BO15|BO16 +2</t>
+        </is>
+      </c>
+      <c r="I3" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">press_engagement</t>
+        </is>
+      </c>
+      <c r="J3" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="O3" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A4" s="107" t="s">
         <v>2576</v>
       </c>
@@ -10447,8 +10528,31 @@
       <c r="G4" s="107" t="s">
         <v>2580</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="H4" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BO03|BO04|BO06|BO07|BO11|BO12|BO14 +2</t>
+        </is>
+      </c>
+      <c r="I4" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">district_engagement</t>
+        </is>
+      </c>
+      <c r="J4" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="O4" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A5" s="107" t="s">
         <v>2581</v>
       </c>
@@ -10470,8 +10574,36 @@
       <c r="G5" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H5" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENERGY +1</t>
+        </is>
+      </c>
+      <c r="I5" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coffee</t>
+        </is>
+      </c>
+      <c r="J5" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L5" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="M5" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A6" s="107" t="s">
         <v>2584</v>
       </c>
@@ -10493,8 +10625,36 @@
       <c r="G6" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H6" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAFFE_CAP +1</t>
+        </is>
+      </c>
+      <c r="I6" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea</t>
+        </is>
+      </c>
+      <c r="J6" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L6" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="M6" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A7" s="107" t="s">
         <v>2587</v>
       </c>
@@ -10516,8 +10676,36 @@
       <c r="G7" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="H7" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DRAW +1</t>
+        </is>
+      </c>
+      <c r="I7" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paperwork_automation</t>
+        </is>
+      </c>
+      <c r="J7" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L7" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="M7" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="107" t="s">
         <v>2590</v>
       </c>
@@ -10539,8 +10727,36 @@
       <c r="G8" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="H8" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TURNS +1</t>
+        </is>
+      </c>
+      <c r="I8" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wristwatch</t>
+        </is>
+      </c>
+      <c r="J8" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L8" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="M8" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A9" s="107" t="s">
         <v>2593</v>
       </c>
@@ -10562,8 +10778,36 @@
       <c r="G9" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H9" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUARD +1</t>
+        </is>
+      </c>
+      <c r="I9" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">meditation</t>
+        </is>
+      </c>
+      <c r="J9" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L9" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage</t>
+        </is>
+      </c>
+      <c r="M9" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A10" s="107" t="s">
         <v>2596</v>
       </c>
@@ -10585,8 +10829,23 @@
       <c r="G10" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I10" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blue_profile</t>
+        </is>
+      </c>
+      <c r="J10" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K10" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A11" s="107" t="s">
         <v>2599</v>
       </c>
@@ -10608,8 +10867,23 @@
       <c r="G11" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I11" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red_profile</t>
+        </is>
+      </c>
+      <c r="J11" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K11" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A12" s="107" t="s">
         <v>2601</v>
       </c>
@@ -10631,8 +10905,23 @@
       <c r="G12" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I12" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blue_background</t>
+        </is>
+      </c>
+      <c r="J12" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K12" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A13" s="107" t="s">
         <v>2604</v>
       </c>
@@ -10654,8 +10943,23 @@
       <c r="G13" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="I13" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red_background</t>
+        </is>
+      </c>
+      <c r="J13" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K13" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="107" t="s">
         <v>2606</v>
       </c>
@@ -10677,8 +10981,23 @@
       <c r="G14" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="I14" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unlock_level_t1</t>
+        </is>
+      </c>
+      <c r="J14" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K14" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A15" s="107" t="s">
         <v>2608</v>
       </c>
@@ -10700,8 +11019,23 @@
       <c r="G15" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I15" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unlock_level_t2</t>
+        </is>
+      </c>
+      <c r="J15" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K15" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A16" s="107" t="s">
         <v>2611</v>
       </c>
@@ -10723,8 +11057,23 @@
       <c r="G16" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I16" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unlock_card_t1</t>
+        </is>
+      </c>
+      <c r="J16" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K16" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="107" t="s">
         <v>2614</v>
       </c>
@@ -10746,8 +11095,23 @@
       <c r="G17" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I17" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unlock_card_t2</t>
+        </is>
+      </c>
+      <c r="J17" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K17" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A18" s="107" t="s">
         <v>2617</v>
       </c>
@@ -10769,8 +11133,23 @@
       <c r="G18" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="I18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unlock_card_t3</t>
+        </is>
+      </c>
+      <c r="J18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A19" s="107" t="s">
         <v>2620</v>
       </c>
@@ -10792,8 +11171,23 @@
       <c r="G19" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="I19" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff_tier</t>
+        </is>
+      </c>
+      <c r="J19" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K19" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="107" t="s">
         <v>2623</v>
       </c>
@@ -10815,8 +11209,23 @@
       <c r="G20" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I20" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">funds_cap</t>
+        </is>
+      </c>
+      <c r="J20" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K20" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A21" s="107" t="s">
         <v>2626</v>
       </c>
@@ -10838,8 +11247,42 @@
       <c r="G21" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DRAW +1</t>
+        </is>
+      </c>
+      <c r="I21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff_draw</t>
+        </is>
+      </c>
+      <c r="J21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="M21" s="108">
+        <v>1</v>
+      </c>
+      <c r="N21" s="108">
+        <v>2</v>
+      </c>
+      <c r="O21" s="108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="107" t="s">
         <v>2630</v>
       </c>
@@ -10861,8 +11304,42 @@
       <c r="G22" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENERGY +1</t>
+        </is>
+      </c>
+      <c r="I22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff_energy</t>
+        </is>
+      </c>
+      <c r="J22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="M22" s="108">
+        <v>1</v>
+      </c>
+      <c r="N22" s="108">
+        <v>3</v>
+      </c>
+      <c r="O22" s="108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="107" t="s">
         <v>2634</v>
       </c>
@@ -10884,8 +11361,42 @@
       <c r="G23" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUARD +1</t>
+        </is>
+      </c>
+      <c r="I23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff_guard</t>
+        </is>
+      </c>
+      <c r="J23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="M23" s="108">
+        <v>1</v>
+      </c>
+      <c r="N23" s="108">
+        <v>5</v>
+      </c>
+      <c r="O23" s="108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A24" s="107" t="s">
         <v>2638</v>
       </c>
@@ -10907,8 +11418,42 @@
       <c r="G24" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAFFE_CAP +1</t>
+        </is>
+      </c>
+      <c r="I24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff_gaffe_cap</t>
+        </is>
+      </c>
+      <c r="J24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="M24" s="108">
+        <v>1</v>
+      </c>
+      <c r="N24" s="108">
+        <v>5</v>
+      </c>
+      <c r="O24" s="108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A25" s="107" t="s">
         <v>2642</v>
       </c>
@@ -10930,8 +11475,42 @@
       <c r="G25" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="H25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TURNS +1</t>
+        </is>
+      </c>
+      <c r="I25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buff_turn</t>
+        </is>
+      </c>
+      <c r="J25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="L25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="M25" s="108">
+        <v>1</v>
+      </c>
+      <c r="N25" s="108">
+        <v>3</v>
+      </c>
+      <c r="O25" s="108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="107" t="s">
         <v>2646</v>
       </c>
@@ -10953,8 +11532,23 @@
       <c r="G26" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="I26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">booster_dinner</t>
+        </is>
+      </c>
+      <c r="J26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A27" s="107" t="s">
         <v>2650</v>
       </c>
@@ -10976,8 +11570,23 @@
       <c r="G27" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
+      <c r="I27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">walking_tour</t>
+        </is>
+      </c>
+      <c r="J27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A28" s="107" t="s">
         <v>2757</v>
       </c>
@@ -10999,8 +11608,23 @@
       <c r="G28" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
+      <c r="I28" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buy_card_t1</t>
+        </is>
+      </c>
+      <c r="J28" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K28" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A29" s="107" t="s">
         <v>2758</v>
       </c>
@@ -11022,8 +11646,23 @@
       <c r="G29" s="109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="68.25" x14ac:dyDescent="0.2">
+      <c r="I29" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buy_card_t2</t>
+        </is>
+      </c>
+      <c r="J29" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K29" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A30" s="107" t="s">
         <v>2759</v>
       </c>
@@ -11044,6 +11683,21 @@
       </c>
       <c r="G30" s="109" t="s">
         <v>13</v>
+      </c>
+      <c r="I30" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buy_card_t3</t>
+        </is>
+      </c>
+      <c r="J30" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="K30" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -27177,7 +27831,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.99609375" customWidth="1"/>
@@ -30175,6 +30829,750 @@
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>2848</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.briefing.surprise_stage</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office — briefing</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Something is coming — you will not know what until you are in the room.</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown in place of a stage's name and opponent when its Reveal In Briefing column is No, so a stage meant as a surprise (an ambush) is not spoiled before the player goes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.level_cooldown</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office — levels</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{count} more level(s) first</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">count</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown on a level still on cooldown when level_gating_enabled is true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.level_unlock_cost</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office — levels</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unlock — {cost} XP</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown on a locked level button when level_gating_enabled is true and the level is affordable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.look_it_over</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office — levels</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Look it over</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was a literal string in OfficeScreen.gd; moved to the Text tab 2026-09-24 alongside the level-gating work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.level_no_id</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This level has no ID.</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A data-integrity guard, not expected to be seen by a player — every real levels.json row has a level_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inventory.button</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office main screen and battle header, Inventory button</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inventory.title</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventory panel, heading</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inventory.empty</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventory panel, when nothing is held</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing here yet. Supplies you buy or are given will appear here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inventory.entry</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventory panel, one item's button</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} ×{count}</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name, count</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.quantity</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You have {count}.</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">count</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.stack_cap</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, when the item has a Stack Cap</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You can carry up to {count}.</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">count</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown only when the Shop tab's Stack Cap is set for this item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.use</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, use button</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.close</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, close button</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.timing.now</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, an item with no stage effect</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes effect immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.timing.stage_next</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, in the Office, Duration Stage</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes effect at the start of your next stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.timing.level_next</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, in the Office, Duration Level</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lasts for the whole of your next level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.timing.stage_now</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, during a stage, Duration Stage</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes effect now, for the rest of this stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.timing.level_now</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, during a stage, Duration Level</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes effect now and lasts for the rest of this level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.used</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message after using an item</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} used.</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.queued</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message after using a Stage item in the Office</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is ready for your next stage.</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.queued_level</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Message after using a Level item in the Office</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} will last through your next level.</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.refused.none_left</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, refusal</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You have none left.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.refused.not_here</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, refusal</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This can't be used here.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Shop tab's Use In Office / Use In Stage cell for this item says No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.refused.no_effect</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, refusal</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This item has no effect set yet.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Shop tab's Grants cell for this item is blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.refused.turn_limit</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, refusal during a stage</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You can't use this again until next turn.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Shop tab's Uses Per Turn cap for this item is reached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.refused.battle_over</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, refusal during a stage</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This stage is already over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.supplies</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office Management, Supplies button and panel heading</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.supplies_blurb</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies go into your inventory. Open the inventory from the Office or during a stage to use them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.item_title</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, one item</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name}  —  {price}</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name, price</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.item_price_xp</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, price part</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{count} XP</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">count</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.item_price_yen</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, price part</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{count} Yen</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">count</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.item_free</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, an item with no price</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Free</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.buy</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, buy button</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.item_bought</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office report after buying</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} added to your inventory.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.out_of_stock</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, item at its Purchase Limit for this level</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Out of Stock</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resets when a level concludes, win or loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.stack_full</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies panel, item at its Stack Cap</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You can't carry any more of these.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shop.item_no_id</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shop — refusals</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This item has no ID.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A data-integrity guard, not expected to be seen by a player.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -10342,7 +10342,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DBCFC6-E562-474C-8005-C80E8AAC1DE0}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.84765625" customWidth="1"/>
@@ -10351,7 +10351,7 @@
     <col min="7" max="7" width="20.04296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A1" s="106" t="s">
         <v>2553</v>
       </c>
@@ -10413,8 +10413,58 @@
           <t xml:space="preserve">Purchase Limit</t>
         </is>
       </c>
-    </row>
-    <row r="2" spans="1:15" ht="108" x14ac:dyDescent="0.2">
+      <c r="P1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player Choice</t>
+        </is>
+      </c>
+      <c r="Q1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 1 Role</t>
+        </is>
+      </c>
+      <c r="R1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 1 Min Tier</t>
+        </is>
+      </c>
+      <c r="S1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 1 Amount</t>
+        </is>
+      </c>
+      <c r="T1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 2 Role</t>
+        </is>
+      </c>
+      <c r="U1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 2 Min Tier</t>
+        </is>
+      </c>
+      <c r="V1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 2 Amount</t>
+        </is>
+      </c>
+      <c r="W1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 3 Role</t>
+        </is>
+      </c>
+      <c r="X1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 3 Min Tier</t>
+        </is>
+      </c>
+      <c r="Y1" s="106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bonus 3 Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="108" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>2566</v>
       </c>
@@ -10438,7 +10488,7 @@
       </c>
       <c r="H2" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">BO01|BO02 +1</t>
+          <t xml:space="preserve">TIER:Party +1</t>
         </is>
       </c>
       <c r="I2" s="107" t="inlineStr">
@@ -10459,8 +10509,30 @@
       <c r="O2" s="108">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="108" x14ac:dyDescent="0.2">
+      <c r="Q2" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Policy Research Assistant</t>
+        </is>
+      </c>
+      <c r="R2" s="108">
+        <v>1</v>
+      </c>
+      <c r="S2" s="108">
+        <v>0</v>
+      </c>
+      <c r="T2" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Policy Research Assistant</t>
+        </is>
+      </c>
+      <c r="U2" s="108">
+        <v>2</v>
+      </c>
+      <c r="V2" s="108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="108" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>2571</v>
       </c>
@@ -10484,7 +10556,7 @@
       </c>
       <c r="H3" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">BO05|BO08|BO09|BO10|BO13|BO15|BO16 +2</t>
+          <t xml:space="preserve">TIER:National +2</t>
         </is>
       </c>
       <c r="I3" s="107" t="inlineStr">
@@ -10505,8 +10577,30 @@
       <c r="O3" s="108">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="94.5" x14ac:dyDescent="0.2">
+      <c r="Q3" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media Spokesperson</t>
+        </is>
+      </c>
+      <c r="R3" s="108">
+        <v>1</v>
+      </c>
+      <c r="S3" s="108">
+        <v>0</v>
+      </c>
+      <c r="T3" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Media Spokesperson</t>
+        </is>
+      </c>
+      <c r="U3" s="108">
+        <v>2</v>
+      </c>
+      <c r="V3" s="108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="94.5" x14ac:dyDescent="0.2">
       <c r="A4" s="107" t="s">
         <v>2576</v>
       </c>
@@ -10530,7 +10624,7 @@
       </c>
       <c r="H4" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">BO03|BO04|BO06|BO07|BO11|BO12|BO14 +2</t>
+          <t xml:space="preserve">TIER:Constituency +2</t>
         </is>
       </c>
       <c r="I4" s="107" t="inlineStr">
@@ -10551,8 +10645,30 @@
       <c r="O4" s="108">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="Q4" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">District Representative</t>
+        </is>
+      </c>
+      <c r="R4" s="108">
+        <v>1</v>
+      </c>
+      <c r="S4" s="108">
+        <v>0</v>
+      </c>
+      <c r="T4" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">District Representative</t>
+        </is>
+      </c>
+      <c r="U4" s="108">
+        <v>2</v>
+      </c>
+      <c r="V4" s="108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A5" s="107" t="s">
         <v>2581</v>
       </c>
@@ -10603,7 +10719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A6" s="107" t="s">
         <v>2584</v>
       </c>
@@ -10654,7 +10770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A7" s="107" t="s">
         <v>2587</v>
       </c>
@@ -10705,7 +10821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="107" t="s">
         <v>2590</v>
       </c>
@@ -10756,7 +10872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A9" s="107" t="s">
         <v>2593</v>
       </c>
@@ -10807,7 +10923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A10" s="107" t="s">
         <v>2596</v>
       </c>
@@ -10845,7 +10961,7 @@
         </is>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A11" s="107" t="s">
         <v>2599</v>
       </c>
@@ -10883,7 +10999,7 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A12" s="107" t="s">
         <v>2601</v>
       </c>
@@ -10921,7 +11037,7 @@
         </is>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A13" s="107" t="s">
         <v>2604</v>
       </c>
@@ -10959,7 +11075,7 @@
         </is>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="107" t="s">
         <v>2606</v>
       </c>
@@ -10997,7 +11113,7 @@
         </is>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A15" s="107" t="s">
         <v>2608</v>
       </c>
@@ -11035,7 +11151,7 @@
         </is>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A16" s="107" t="s">
         <v>2611</v>
       </c>
@@ -11073,7 +11189,7 @@
         </is>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="107" t="s">
         <v>2614</v>
       </c>
@@ -11111,7 +11227,7 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A18" s="107" t="s">
         <v>2617</v>
       </c>
@@ -11149,7 +11265,7 @@
         </is>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A19" s="107" t="s">
         <v>2620</v>
       </c>
@@ -11187,7 +11303,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="107" t="s">
         <v>2623</v>
       </c>
@@ -11225,7 +11341,7 @@
         </is>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A21" s="107" t="s">
         <v>2626</v>
       </c>
@@ -11282,7 +11398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="107" t="s">
         <v>2630</v>
       </c>
@@ -11339,7 +11455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="107" t="s">
         <v>2634</v>
       </c>
@@ -11396,7 +11512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A24" s="107" t="s">
         <v>2638</v>
       </c>
@@ -11453,7 +11569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A25" s="107" t="s">
         <v>2642</v>
       </c>
@@ -11510,7 +11626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="107" t="s">
         <v>2646</v>
       </c>
@@ -11539,7 +11655,7 @@
       </c>
       <c r="J26" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="K26" s="107" t="inlineStr">
@@ -11547,8 +11663,18 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="H26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER:National +2</t>
+        </is>
+      </c>
+      <c r="P26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A27" s="107" t="s">
         <v>2650</v>
       </c>
@@ -11577,7 +11703,7 @@
       </c>
       <c r="J27" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="K27" s="107" t="inlineStr">
@@ -11585,8 +11711,18 @@
           <t xml:space="preserve">No</t>
         </is>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
+      <c r="H27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TIER:Constituency +1</t>
+        </is>
+      </c>
+      <c r="P27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A28" s="107" t="s">
         <v>2757</v>
       </c>
@@ -11624,7 +11760,7 @@
         </is>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A29" s="107" t="s">
         <v>2758</v>
       </c>
@@ -11662,7 +11798,7 @@
         </is>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A30" s="107" t="s">
         <v>2759</v>
       </c>
@@ -27831,7 +27967,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.99609375" customWidth="1"/>
@@ -31572,6 +31708,33 @@
       <c r="E250" t="inlineStr">
         <is>
           <t xml:space="preserve">A data-integrity guard, not expected to be seen by a player.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">item.choose_heading</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item pop-up, Player Choice item, picker heading</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name}  —  choose a group</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown instead of the ordinary pop-up when the Shop tab's Player Choice cell for this item is Yes.</t>
         </is>
       </c>
     </row>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -27967,7 +27967,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.99609375" customWidth="1"/>
@@ -31735,6 +31735,184 @@
       <c r="E251" t="inlineStr">
         <is>
           <t xml:space="preserve">Shown instead of the ordinary pop-up when the Shop tab's Player Choice cell for this item is Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.resume_level</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office, Start button, when a saved run stopped partway through a level</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resume level</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes the player straight back into the level they were playing, at the stage they had reached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.new_game</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office Management, button; and the heading of the warning it opens</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New game</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.new_game_warning</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New game, the warning before the run is thrown away</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Starting a new game ends this run. Your standing, cards, staff and items all go back to the start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.new_game_confirm</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New game warning, confirm button</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Start over</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">office.new_game_started</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Office report line, after a protagonist is chosen</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A new run begins. Welcome to the Office, {name}.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new_game.title</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Game screen heading</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Choose your legislator</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shown on first launch, and after New game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new_game.blurb</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Game screen, line under the heading</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who are you in Parliament? You play the whole run as the one you choose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new_game.no_party</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Game screen, a protagonist with no party set in player.json</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No party yet</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All four protagonists are placeholders until the cast is decided (data/player.json).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new_game.choose</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Game screen, button under each protagonist</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Play as {name}</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
     </row>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -27841,7 +27841,6 @@
         <v>895</v>
       </c>
       <c r="D2" s="80">
-        <f>Segments!F4</f>
         <v>15</v>
       </c>
       <c r="E2" s="4">
@@ -27874,7 +27873,6 @@
         <v>1091</v>
       </c>
       <c r="D3" s="80">
-        <f>(Segments!F2+Segments!F4+Segments!F5+Segments!F6)/5</f>
         <v>6</v>
       </c>
       <c r="E3" s="4">
@@ -27936,7 +27934,6 @@
         <v>1097</v>
       </c>
       <c r="D5" s="80">
-        <f>Segments!F3</f>
         <v>10</v>
       </c>
       <c r="E5" s="4">

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -27841,6 +27841,7 @@
         <v>895</v>
       </c>
       <c r="D2" s="80">
+        <f>Segments!F4</f>
         <v>15</v>
       </c>
       <c r="E2" s="4">
@@ -27873,6 +27874,7 @@
         <v>1091</v>
       </c>
       <c r="D3" s="80">
+        <f>(Segments!F2+Segments!F4+Segments!F5+Segments!F6)/5</f>
         <v>6</v>
       </c>
       <c r="E3" s="4">
@@ -27934,6 +27936,7 @@
         <v>1097</v>
       </c>
       <c r="D5" s="80">
+        <f>Segments!F3</f>
         <v>10</v>
       </c>
       <c r="E5" s="4">

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7605" uniqueCount="3140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7609" uniqueCount="3144">
   <si>
     <t>Staff ID</t>
   </si>
@@ -9482,6 +9482,18 @@
   </si>
   <si>
     <t>bonus_if_target_segment_ge_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.upcoming_intent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle - opponent row, shown only after a card reveals the move after next (C12 Head Count)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Then: {intent}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intent</t>
   </si>
 </sst>
 </file>
@@ -28675,7 +28687,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -32280,6 +32292,20 @@
       </c>
       <c r="D260" t="s">
         <v>1193</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" t="s">
+        <v>3140</v>
+      </c>
+      <c r="B261" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C261" t="s">
+        <v>3142</v>
+      </c>
+      <c r="D261" t="s">
+        <v>3143</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -38,6 +38,7 @@
     <sheet name="Question Themes" sheetId="22" r:id="rId23"/>
     <sheet name="Visitors" sheetId="24" r:id="rId24"/>
     <sheet name="Visitor Questions" sheetId="25" r:id="rId25"/>
+    <sheet name="Opponent Cues" sheetId="26" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Cards!$A$1:$T$55</definedName>
@@ -41086,6 +41087,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="9" width="40" customWidth="1"/>
+    <col min="10" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="17" max="17" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cue ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Suit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Opponent ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Cue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Cue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Cue 3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Cue 4</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cue 5</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Max words</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Word limit</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7609" uniqueCount="3144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7634" uniqueCount="3169">
   <si>
     <t>Staff ID</t>
   </si>
@@ -9495,6 +9495,82 @@
   </si>
   <si>
     <t xml:space="preserve">intent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office_hours.cannot_start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Hours — notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This room could not open:
+• {problems}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office_hours.continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Hours — button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office_hours.done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Hours — outcome title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office_hours.summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Hours — outcome body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{correct} of {visited} won over.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">correct, visited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.question_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle — a room whose cards answer a drawn question but is not shaped like a press conference (e.g. Town Hall)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They ask: {question}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new_game.starting_stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Game screen, heading over each protagonist's starting numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting numbers:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new_game.stat_line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Game screen, one line per starting number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name}: {value}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name, value</t>
   </si>
 </sst>
 </file>
@@ -28688,7 +28764,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E261"/>
+  <dimension ref="A1:E268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -32307,6 +32383,95 @@
       </c>
       <c r="D261" t="s">
         <v>3143</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B262" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C262" t="s">
+        <v>3146</v>
+      </c>
+      <c r="D262" t="s">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B263" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C263" t="s">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" t="s">
+        <v>3151</v>
+      </c>
+      <c r="B264" t="s">
+        <v>3152</v>
+      </c>
+      <c r="C264" t="s">
+        <v>3153</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" t="s">
+        <v>3154</v>
+      </c>
+      <c r="B265" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C265" t="s">
+        <v>3156</v>
+      </c>
+      <c r="D265" t="s">
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" t="s">
+        <v>3158</v>
+      </c>
+      <c r="B266" t="s">
+        <v>3159</v>
+      </c>
+      <c r="C266" t="s">
+        <v>3160</v>
+      </c>
+      <c r="D266" t="s">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B267" t="s">
+        <v>3163</v>
+      </c>
+      <c r="C267" t="s">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B268" t="s">
+        <v>3166</v>
+      </c>
+      <c r="C268" t="s">
+        <v>3167</v>
+      </c>
+      <c r="D268" t="s">
+        <v>3168</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7634" uniqueCount="3169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="3178">
   <si>
     <t>Staff ID</t>
   </si>
@@ -9571,6 +9571,33 @@
   </si>
   <si>
     <t xml:space="preserve">name, value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro (title) screen, heading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coliseum of Parliament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro.continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro (title) screen, button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intro.new_game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intro (title) screen, button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Game</t>
   </si>
 </sst>
 </file>
@@ -28764,7 +28791,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -32472,6 +32499,39 @@
       </c>
       <c r="D268" t="s">
         <v>3168</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B269" t="s">
+        <v>3170</v>
+      </c>
+      <c r="C269" t="s">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B270" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C270" t="s">
+        <v>3174</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B271" t="s">
+        <v>3176</v>
+      </c>
+      <c r="C271" t="s">
+        <v>3177</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16903" uniqueCount="4722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16918" uniqueCount="4737">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14231,6 +14231,51 @@
   </si>
   <si>
     <t xml:space="preserve">buy_card_t3.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firing Cost from Funds (Yen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each role can hold one hire at a time. Hiring, upgrading and firing are all paid from Funds — firing costs a severance, and someone you fire will never work for you again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.fire_staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office · Recruitment shop, a filled role's row — button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.fire_staff_warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office · Recruitment shop, the warning before firing someone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firing {name} costs {cost} Yen in severance. They will never work for you again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name, cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.fire_staff_confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire warning, confirm button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.staff_fired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office · Recruitment shop, a role's candidate list — someone fired earlier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fired — will not work for you again.</t>
   </si>
 </sst>
 </file>
@@ -17193,7 +17238,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -17206,9 +17251,10 @@
     <col min="10" max="10" width="26" customWidth="1"/>
     <col min="11" max="11" width="34" customWidth="1"/>
     <col min="12" max="12" width="40" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1">
+    <row r="1" spans="1:13" ht="30" customHeight="1">
       <c r="A1" s="99" t="s">
         <v>0</v>
       </c>
@@ -17245,8 +17291,11 @@
       <c r="L1" s="99" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="99" t="s">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="84" t="s">
         <v>11</v>
       </c>
@@ -17283,8 +17332,11 @@
       <c r="L2" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="100">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="84" t="s">
         <v>15</v>
       </c>
@@ -17321,8 +17373,11 @@
       <c r="L3" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="100">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="84" t="s">
         <v>18</v>
       </c>
@@ -17359,8 +17414,11 @@
       <c r="L4" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="100">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="84" t="s">
         <v>20</v>
       </c>
@@ -17397,8 +17455,11 @@
       <c r="L5" s="84" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="100">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="84" t="s">
         <v>24</v>
       </c>
@@ -17435,8 +17496,11 @@
       <c r="L6" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="100">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="84" t="s">
         <v>26</v>
       </c>
@@ -17473,8 +17537,11 @@
       <c r="L7" s="84" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="100">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="84" t="s">
         <v>30</v>
       </c>
@@ -17511,8 +17578,11 @@
       <c r="L8" s="84" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8" s="100">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="84" t="s">
         <v>33</v>
       </c>
@@ -17549,8 +17619,11 @@
       <c r="L9" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9" s="100">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="84" t="s">
         <v>36</v>
       </c>
@@ -17587,8 +17660,11 @@
       <c r="L10" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10" s="100">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="84" t="s">
         <v>39</v>
       </c>
@@ -17625,8 +17701,11 @@
       <c r="L11" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11" s="100">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="84" t="s">
         <v>41</v>
       </c>
@@ -17663,8 +17742,11 @@
       <c r="L12" s="84" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12" s="100">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="84" t="s">
         <v>45</v>
       </c>
@@ -17701,8 +17783,11 @@
       <c r="L13" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13" s="100">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="84" t="s">
         <v>47</v>
       </c>
@@ -17739,8 +17824,11 @@
       <c r="L14" s="84" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14" s="100">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="84" t="s">
         <v>50</v>
       </c>
@@ -17777,8 +17865,11 @@
       <c r="L15" s="84" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15" s="100">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="84" t="s">
         <v>53</v>
       </c>
@@ -17815,8 +17906,11 @@
       <c r="L16" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="100">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="84" t="s">
         <v>56</v>
       </c>
@@ -17853,8 +17947,11 @@
       <c r="L17" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17" s="100">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="84" t="s">
         <v>59</v>
       </c>
@@ -17891,8 +17988,11 @@
       <c r="L18" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18" s="100">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="84" t="s">
         <v>61</v>
       </c>
@@ -17929,8 +18029,11 @@
       <c r="L19" s="84" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19" s="100">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="84" t="s">
         <v>64</v>
       </c>
@@ -17967,8 +18070,11 @@
       <c r="L20" s="101" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20" s="100">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="84" t="s">
         <v>66</v>
       </c>
@@ -18005,8 +18111,11 @@
       <c r="L21" s="84" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21" s="100">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="84" t="s">
         <v>69</v>
       </c>
@@ -18042,6 +18151,9 @@
       </c>
       <c r="L22" s="84" t="s">
         <v>71</v>
+      </c>
+      <c r="M22" s="100">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
@@ -33424,7 +33536,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -36352,7 +36464,7 @@
         <v>2816</v>
       </c>
       <c r="C204" t="s">
-        <v>2817</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -37165,6 +37277,53 @@
       </c>
       <c r="C271" t="s">
         <v>3177</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" t="s">
+        <v>4724</v>
+      </c>
+      <c r="B272" t="s">
+        <v>4725</v>
+      </c>
+      <c r="C272" t="s">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" t="s">
+        <v>4727</v>
+      </c>
+      <c r="B273" t="s">
+        <v>4728</v>
+      </c>
+      <c r="C273" t="s">
+        <v>4729</v>
+      </c>
+      <c r="D273" t="s">
+        <v>4730</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" t="s">
+        <v>4731</v>
+      </c>
+      <c r="B274" t="s">
+        <v>4732</v>
+      </c>
+      <c r="C274" t="s">
+        <v>4733</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" t="s">
+        <v>4734</v>
+      </c>
+      <c r="B275" t="s">
+        <v>4735</v>
+      </c>
+      <c r="C275" t="s">
+        <v>4736</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -33937,20 +33937,6 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>1184</v>
-      </c>
-    </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
         <v>1185</v>
@@ -34323,38 +34309,6 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>1259</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>1262</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1235</v>
-      </c>
-      <c r="E53" s="13"/>
-    </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
         <v>1264</v>
@@ -35916,23 +35870,6 @@
         <v>1210</v>
       </c>
       <c r="E165" s="13"/>
-    </row>
-    <row r="166" spans="1:5">
-      <c r="A166" t="s">
-        <v>1543</v>
-      </c>
-      <c r="B166" t="s">
-        <v>1533</v>
-      </c>
-      <c r="C166" s="13" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D166" t="s">
-        <v>1210</v>
-      </c>
-      <c r="E166" s="13" t="s">
-        <v>1545</v>
-      </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16918" uniqueCount="4737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16978" uniqueCount="4797">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14276,6 +14276,186 @@
   </si>
   <si>
     <t xml:space="preserve">Fired — will not work for you again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiban: town hall trigger (≤)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constituency support at or below this inserts a Town Hall into the level queue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support: funding freeze (≤)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support at or below this freezes Funds income until it rises back above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support: steering committee (&lt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support below this inserts the Steering Committee check-in (ST22) into the level queue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support: allied buff (&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support above this grants M09 (Party Backing) free, on top of anything owned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support: debuff (&lt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support below this grants M10 (Cold Shoulder) free, on top of anything owned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaffes: lifetime penalty threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifetime gaffes at or above this apply the one-time Jiban penalty below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaffes: lifetime penalty jiban delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied once, the moment lifetime gaffes cross the threshold above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding Freeze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資金凍結</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shikin Tōketsu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding is frozen while party support is at or below the Balance tab's own threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUNDS_INCOME_FREEZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ST22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party Steering Committee Check-In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">党運営委員会面談</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tō Un'ei Iinkai Mendan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VI04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party Member A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">党員A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tōin A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steering Committee Member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VQ04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where do you stand on the party's current platform?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fully behind it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I have reservations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'd rather not say</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Against it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good. That's what we like to hear.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...I see.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nods, satisfied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frowns, taking note.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger_alert_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office — a popup on return, when a crisis trigger fired or resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since your last visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.town_hall.entered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office — crisis alert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constituency support fell to {count} — a Town Hall has been added to your schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.town_hall.left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constituency support has recovered — no Town Hall is pending.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.steering_committee.entered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support fell to {count} — the Steering Committee wants to see you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.steering_committee.left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support has recovered — the Steering Committee is no longer waiting.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.funding_freeze.entered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support hit zero. Funding is frozen until it recovers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.funding_freeze.left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Party support has recovered. Funding has resumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.trigger.gaffe_penalty.entered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{count} gaffes this run — Constituency support took a {amount} hit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count, amount</t>
   </si>
 </sst>
 </file>
@@ -33536,7 +33716,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E283"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -37261,6 +37441,103 @@
       </c>
       <c r="C275" t="s">
         <v>4736</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" t="s">
+        <v>4777</v>
+      </c>
+      <c r="B276" t="s">
+        <v>4778</v>
+      </c>
+      <c r="C276" t="s">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" t="s">
+        <v>4780</v>
+      </c>
+      <c r="B277" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C277" t="s">
+        <v>4782</v>
+      </c>
+      <c r="D277" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B278" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C278" t="s">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" t="s">
+        <v>4786</v>
+      </c>
+      <c r="B279" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C279" t="s">
+        <v>4787</v>
+      </c>
+      <c r="D279" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" t="s">
+        <v>4788</v>
+      </c>
+      <c r="B280" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C280" t="s">
+        <v>4789</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" t="s">
+        <v>4790</v>
+      </c>
+      <c r="B281" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C281" t="s">
+        <v>4791</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" t="s">
+        <v>4792</v>
+      </c>
+      <c r="B282" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C282" t="s">
+        <v>4793</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" t="s">
+        <v>4794</v>
+      </c>
+      <c r="B283" t="s">
+        <v>4781</v>
+      </c>
+      <c r="C283" t="s">
+        <v>4795</v>
+      </c>
+      <c r="D283" t="s">
+        <v>4796</v>
       </c>
     </row>
   </sheetData>
@@ -41867,7 +42144,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -41972,6 +42249,83 @@
       </c>
       <c r="C9" s="3" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>4737</v>
+      </c>
+      <c r="B10" s="4">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>4739</v>
+      </c>
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>4741</v>
+      </c>
+      <c r="B12" s="4">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>4743</v>
+      </c>
+      <c r="B13" s="4">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>4745</v>
+      </c>
+      <c r="B14" s="4">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>4747</v>
+      </c>
+      <c r="B15" s="4">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>4749</v>
+      </c>
+      <c r="B16" s="4">
+        <v>-15</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>4750</v>
       </c>
     </row>
   </sheetData>
@@ -45766,7 +46120,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -45870,6 +46224,32 @@
         <v>3068</v>
       </c>
       <c r="H4" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>4762</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4763</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4764</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4765</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4766</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4757</v>
+      </c>
+      <c r="G5" t="s">
+        <v>3068</v>
+      </c>
+      <c r="H5" t="s">
         <v>3069</v>
       </c>
     </row>
@@ -45880,7 +46260,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -46033,6 +46413,44 @@
       </c>
       <c r="L4" t="s">
         <v>3091</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>4767</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4762</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4768</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4769</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4770</v>
+      </c>
+      <c r="F5" t="s">
+        <v>4771</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4772</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3087</v>
+      </c>
+      <c r="I5" t="s">
+        <v>4773</v>
+      </c>
+      <c r="J5" t="s">
+        <v>4774</v>
+      </c>
+      <c r="K5" t="s">
+        <v>4775</v>
+      </c>
+      <c r="L5" t="s">
+        <v>4776</v>
       </c>
     </row>
   </sheetData>
@@ -75936,7 +76354,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AP46"/>
+  <dimension ref="A1:AP47"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -79531,6 +79949,125 @@
       <c r="AG46" s="81"/>
       <c r="AH46" s="81"/>
     </row>
+    <row r="47" spans="1:42" ht="26.25" customHeight="1">
+      <c r="A47" s="4" t="s">
+        <v>4757</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>4758</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>4759</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>4760</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="H47" s="4">
+        <v>10</v>
+      </c>
+      <c r="I47" s="4">
+        <v>10</v>
+      </c>
+      <c r="J47" s="5">
+        <v>1</v>
+      </c>
+      <c r="K47" s="4">
+        <v>10</v>
+      </c>
+      <c r="L47" s="4">
+        <v>5</v>
+      </c>
+      <c r="M47" s="4">
+        <v>5</v>
+      </c>
+      <c r="N47" s="4">
+        <v>7</v>
+      </c>
+      <c r="O47" s="4">
+        <v>0</v>
+      </c>
+      <c r="P47" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
+      <c r="R47" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="S47" s="5">
+        <v>0</v>
+      </c>
+      <c r="T47" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="U47" s="5">
+        <v>0</v>
+      </c>
+      <c r="V47" s="5">
+        <v>0</v>
+      </c>
+      <c r="W47" s="5">
+        <v>1</v>
+      </c>
+      <c r="X47" s="4" t="s">
+        <v>4761</v>
+      </c>
+      <c r="Y47" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="73">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="4">
+        <v>30</v>
+      </c>
+      <c r="AC47" s="4">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="4" t="s">
+        <v>2996</v>
+      </c>
+      <c r="AJ47" s="4" t="s">
+        <v>2992</v>
+      </c>
+      <c r="AL47" s="4" t="s">
+        <v>2993</v>
+      </c>
+      <c r="AM47" s="4" t="s">
+        <v>2994</v>
+      </c>
+      <c r="AO47" s="4" t="s">
+        <v>2995</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -87629,7 +88166,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -88959,6 +89496,35 @@
         <v>10</v>
       </c>
     </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="90" t="s">
+        <v>4751</v>
+      </c>
+      <c r="B33" s="90" t="s">
+        <v>4752</v>
+      </c>
+      <c r="C33" s="95" t="s">
+        <v>4753</v>
+      </c>
+      <c r="D33" s="90" t="s">
+        <v>4754</v>
+      </c>
+      <c r="G33" s="88" t="s">
+        <v>4755</v>
+      </c>
+      <c r="H33" s="96">
+        <v>0</v>
+      </c>
+      <c r="I33" s="96">
+        <v>0</v>
+      </c>
+      <c r="J33" s="96">
+        <v>0</v>
+      </c>
+      <c r="K33" s="90" t="s">
+        <v>4756</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16978" uniqueCount="4797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16983" uniqueCount="4802">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14456,6 +14456,21 @@
   </si>
   <si>
     <t xml:space="preserve">count, amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMITTEE SIZE BY DIFFICULTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very Hard</t>
   </si>
 </sst>
 </file>
@@ -42144,7 +42159,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -42326,6 +42341,55 @@
       </c>
       <c r="C16" s="3" t="s">
         <v>4750</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>4798</v>
+      </c>
+      <c r="B18" s="4">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>4799</v>
+      </c>
+      <c r="B19" s="4">
+        <v>6</v>
+      </c>
+      <c r="C19" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>4800</v>
+      </c>
+      <c r="B20" s="4">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>4801</v>
+      </c>
+      <c r="B21" s="4">
+        <v>8</v>
+      </c>
+      <c r="C21" s="4">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -77157,16 +77221,16 @@
         <v>6</v>
       </c>
       <c r="L7" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" s="4">
         <v>5</v>
       </c>
       <c r="O7" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P7" s="4">
         <v>50</v>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16983" uniqueCount="4802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16984" uniqueCount="4803">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14471,6 +14471,9 @@
   </si>
   <si>
     <t xml:space="preserve">Very Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reset</t>
   </si>
 </sst>
 </file>
@@ -42159,7 +42162,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -42341,55 +42344,6 @@
       </c>
       <c r="C16" s="3" t="s">
         <v>4750</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>4797</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>4798</v>
-      </c>
-      <c r="B18" s="4">
-        <v>5</v>
-      </c>
-      <c r="C18" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>4799</v>
-      </c>
-      <c r="B19" s="4">
-        <v>6</v>
-      </c>
-      <c r="C19" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>4800</v>
-      </c>
-      <c r="B20" s="4">
-        <v>7</v>
-      </c>
-      <c r="C20" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>4801</v>
-      </c>
-      <c r="B21" s="4">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -76679,16 +76633,16 @@
         <v>0</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ2" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL2" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM2" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO2" s="4" t="s">
         <v>2995</v>
@@ -77658,16 +77612,16 @@
         <v>0</v>
       </c>
       <c r="AI10" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ10" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL10" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM10" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO10" s="4" t="s">
         <v>2995</v>
@@ -77780,16 +77734,16 @@
         <v>0</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ11" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL11" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM11" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO11" s="4" t="s">
         <v>2995</v>
@@ -77902,16 +77856,16 @@
         <v>0</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ12" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL12" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM12" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO12" s="4" t="s">
         <v>2995</v>
@@ -78024,16 +77978,16 @@
         <v>0</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ13" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL13" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM13" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO13" s="4" t="s">
         <v>2995</v>
@@ -78146,16 +78100,16 @@
         <v>0</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ14" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL14" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM14" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO14" s="4" t="s">
         <v>2995</v>
@@ -78268,16 +78222,16 @@
         <v>0</v>
       </c>
       <c r="AI15" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ15" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL15" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM15" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO15" s="4" t="s">
         <v>2995</v>
@@ -78390,16 +78344,16 @@
         <v>0</v>
       </c>
       <c r="AI16" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ16" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL16" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM16" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO16" s="4" t="s">
         <v>2995</v>
@@ -78512,16 +78466,16 @@
         <v>0</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ17" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL17" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM17" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO17" s="4" t="s">
         <v>2995</v>
@@ -78634,16 +78588,16 @@
         <v>0</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ18" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL18" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM18" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO18" s="4" t="s">
         <v>2995</v>
@@ -78756,16 +78710,16 @@
         <v>-10</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>2991</v>
+        <v>2996</v>
       </c>
       <c r="AJ19" s="4" t="s">
         <v>2992</v>
       </c>
       <c r="AL19" s="4" t="s">
-        <v>2993</v>
+        <v>4802</v>
       </c>
       <c r="AM19" s="4" t="s">
-        <v>2994</v>
+        <v>361</v>
       </c>
       <c r="AO19" s="4" t="s">
         <v>2995</v>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16984" uniqueCount="4803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16985" uniqueCount="4804">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14474,6 +14474,9 @@
   </si>
   <si>
     <t xml:space="preserve">reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss Ends Level</t>
   </si>
 </sst>
 </file>
@@ -76372,7 +76375,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AP47"/>
+  <dimension ref="A1:AQ47"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -76525,6 +76528,9 @@
       <c r="AP1" s="2" t="s">
         <v>2990</v>
       </c>
+      <c r="AQ1" s="2" t="s">
+        <v>4803</v>
+      </c>
     </row>
     <row r="2" spans="1:42" ht="26.25" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -77016,6 +77022,9 @@
       <c r="AO5" s="4" t="s">
         <v>2999</v>
       </c>
+      <c r="AQ5" s="4" t="s">
+        <v>2995</v>
+      </c>
     </row>
     <row r="6" spans="1:42" ht="26.25" customHeight="1">
       <c r="A6" s="4" t="s">
@@ -78850,6 +78859,9 @@
         <v>2995</v>
       </c>
       <c r="AP20" s="4" t="s">
+        <v>2995</v>
+      </c>
+      <c r="AQ20" s="4" t="s">
         <v>2995</v>
       </c>
     </row>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16985" uniqueCount="4804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16994" uniqueCount="4813">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14477,6 +14477,33 @@
   </si>
   <si>
     <t xml:space="preserve">Loss Ends Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.card_unlocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office report after buying a random-tier card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} unlocked and added to your collection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.no_cards_left_at_tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop — refusals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every Tier {tier} card is already yours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
   </si>
 </sst>
 </file>
@@ -16213,7 +16240,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DBCFC6-E562-474C-8005-C80E8AAC1DE0}">
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
@@ -16298,6 +16325,9 @@
       <c r="Y1" s="106" t="s">
         <v>3021</v>
       </c>
+      <c r="Z1" s="106" t="s">
+        <v>4804</v>
+      </c>
     </row>
     <row r="2" spans="1:25" ht="135">
       <c r="A2" s="107" t="s">
@@ -17366,6 +17396,9 @@
       <c r="K28" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="Z28" s="108">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="75">
       <c r="A29" s="107" t="s">
@@ -17398,6 +17431,9 @@
       <c r="K29" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="Z29" s="108">
+        <v>2</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="75">
       <c r="A30" s="107" t="s">
@@ -17429,6 +17465,9 @@
       </c>
       <c r="K30" s="107" t="s">
         <v>2995</v>
+      </c>
+      <c r="Z30" s="108">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -33737,7 +33776,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -37559,6 +37598,34 @@
       </c>
       <c r="D283" t="s">
         <v>4796</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" t="s">
+        <v>4805</v>
+      </c>
+      <c r="B284" t="s">
+        <v>4806</v>
+      </c>
+      <c r="C284" t="s">
+        <v>4807</v>
+      </c>
+      <c r="D284" t="s">
+        <v>4808</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" t="s">
+        <v>4809</v>
+      </c>
+      <c r="B285" t="s">
+        <v>4810</v>
+      </c>
+      <c r="C285" t="s">
+        <v>4811</v>
+      </c>
+      <c r="D285" t="s">
+        <v>4812</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16994" uniqueCount="4813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17018" uniqueCount="4837">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14504,6 +14504,78 @@
   </si>
   <si>
     <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlocks Recruitment Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funds Cap Increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">office.recruitment_tier_locked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff panel, candidate above the unlocked recruitment tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not open to recruitment yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.no_levels_left_at_tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop — refusals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every Tier {tier} level is already open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.level_unlocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office report after buying a random-tier level unlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{name} unlocked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.recruitment_tier_maxed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop — refusals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every recruitment tier is already open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.recruitment_tier_unlocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office report after buying a staff recruitment tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A new staff recruitment tier is open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.funds_cap_increased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office report after buying a Funds cap increase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funds cap raised by {count}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count</t>
   </si>
 </sst>
 </file>
@@ -16240,7 +16312,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6DBCFC6-E562-474C-8005-C80E8AAC1DE0}">
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
@@ -16328,6 +16400,15 @@
       <c r="Z1" s="106" t="s">
         <v>4804</v>
       </c>
+      <c r="AA1" s="106" t="s">
+        <v>4813</v>
+      </c>
+      <c r="AB1" s="106" t="s">
+        <v>4814</v>
+      </c>
+      <c r="AC1" s="106" t="s">
+        <v>4815</v>
+      </c>
     </row>
     <row r="2" spans="1:25" ht="135">
       <c r="A2" s="107" t="s">
@@ -16861,6 +16942,9 @@
       <c r="K14" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="AA14" s="108">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:25" ht="30">
       <c r="A15" s="107" t="s">
@@ -16893,6 +16977,9 @@
       <c r="K15" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="AA15" s="108">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:25" ht="60">
       <c r="A16" s="107" t="s">
@@ -16925,6 +17012,9 @@
       <c r="K16" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="Z16" s="108">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="60">
       <c r="A17" s="107" t="s">
@@ -16957,6 +17047,9 @@
       <c r="K17" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="Z17" s="108">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="60">
       <c r="A18" s="107" t="s">
@@ -16989,6 +17082,9 @@
       <c r="K18" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="Z18" s="108">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="60">
       <c r="A19" s="107" t="s">
@@ -17021,6 +17117,9 @@
       <c r="K19" s="107" t="s">
         <v>2995</v>
       </c>
+      <c r="AB19" s="107" t="s">
+        <v>2999</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="45">
       <c r="A20" s="107" t="s">
@@ -17052,6 +17151,9 @@
       </c>
       <c r="K20" s="107" t="s">
         <v>2995</v>
+      </c>
+      <c r="AC20" s="108">
+        <v>100000</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="60">
@@ -33776,7 +33878,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -37626,6 +37728,81 @@
       </c>
       <c r="D285" t="s">
         <v>4812</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B286" t="s">
+        <v>4817</v>
+      </c>
+      <c r="C286" t="s">
+        <v>4818</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" t="s">
+        <v>4819</v>
+      </c>
+      <c r="B287" t="s">
+        <v>4820</v>
+      </c>
+      <c r="C287" t="s">
+        <v>4821</v>
+      </c>
+      <c r="D287" t="s">
+        <v>4822</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" t="s">
+        <v>4823</v>
+      </c>
+      <c r="B288" t="s">
+        <v>4824</v>
+      </c>
+      <c r="C288" t="s">
+        <v>4825</v>
+      </c>
+      <c r="D288" t="s">
+        <v>4826</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" t="s">
+        <v>4827</v>
+      </c>
+      <c r="B289" t="s">
+        <v>4828</v>
+      </c>
+      <c r="C289" t="s">
+        <v>4829</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" t="s">
+        <v>4830</v>
+      </c>
+      <c r="B290" t="s">
+        <v>4831</v>
+      </c>
+      <c r="C290" t="s">
+        <v>4832</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" t="s">
+        <v>4833</v>
+      </c>
+      <c r="B291" t="s">
+        <v>4834</v>
+      </c>
+      <c r="C291" t="s">
+        <v>4835</v>
+      </c>
+      <c r="D291" t="s">
+        <v>4836</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17018" uniqueCount="4837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17024" uniqueCount="4843">
   <si>
     <t>Staff ID</t>
   </si>
@@ -14576,6 +14576,24 @@
   </si>
   <si>
     <t xml:space="preserve">count</t>
+  </si>
+  <si>
+    <t>shop.card_reveal_title</t>
+  </si>
+  <si>
+    <t>Office — heading shown when an SH15-17/27-29 purchase reveals the card</t>
+  </si>
+  <si>
+    <t>New Card!</t>
+  </si>
+  <si>
+    <t>shop.card_reveal_confirm</t>
+  </si>
+  <si>
+    <t>Office — button that dismisses the card reveal pop-up</t>
+  </si>
+  <si>
+    <t>Nice.</t>
   </si>
 </sst>
 </file>
@@ -33878,7 +33896,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -37803,6 +37821,28 @@
       </c>
       <c r="D291" t="s">
         <v>4836</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" t="s">
+        <v>4837</v>
+      </c>
+      <c r="B292" t="s">
+        <v>4838</v>
+      </c>
+      <c r="C292" t="s">
+        <v>4839</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" t="s">
+        <v>4840</v>
+      </c>
+      <c r="B293" t="s">
+        <v>4841</v>
+      </c>
+      <c r="C293" t="s">
+        <v>4842</v>
       </c>
     </row>
   </sheetData>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="84" documentId="11_E3793ECF83B57D86E1C6C4BB085A2C099D480AFB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC69C414-1FBE-460B-8E29-BA63A374DE9D}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="0" windowWidth="26145" windowHeight="14670" tabRatio="666" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="666" firstSheet="15" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,20 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Cards!$A$1:$T$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Opponents!$A$1:$T$1000</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -14670,6 +14683,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -40781,7 +40798,7 @@
         <v>6</v>
       </c>
       <c r="N34" s="30">
-        <f t="shared" ref="N34:N65" si="11">MAX(I34:M34)</f>
+        <f t="shared" ref="N34:N55" si="11">MAX(I34:M34)</f>
         <v>7</v>
       </c>
     </row>

--- a/design/CoP_Starter_Card_Stage_Data.xlsx
+++ b/design/CoP_Starter_Card_Stage_Data.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17544" uniqueCount="4606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17575" uniqueCount="4637">
   <si>
     <t>Level ID</t>
   </si>
@@ -13885,6 +13885,99 @@
   </si>
   <si>
     <t>The right time will come...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Say what you actually did.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut the spin. Give me facts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Own it, or don't say it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's not an answer. Try again.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results, not promises. Show me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's the plain truth. Good.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You own your record. I respect that.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight answer. That's rare, and welcome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No spin needed. That worked.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's someone I can trust.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My record speaks. I stand by it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I don't dodge, and I won't start.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Say what you like. Facts don't move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I answer for my own work only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing to hide. Look as long as you want.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soon — I'm working on it personally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's not really up to me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never, if I have anything to say about it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask my staff, not me.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I like the sound of that!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That's not the answer I wanted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grins and gives a thumbs up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sighs and looks away.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Let's talk details after the visit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not today, but thank you.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolutely, sign me up right now.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why would I need a steam shovel?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wonderful! I'll have my people call yours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Fine. I'll find another buyer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shakes hands enthusiastically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crosses arms, unimpressed.</t>
   </si>
 </sst>
 </file>
@@ -47877,31 +47970,31 @@
         <v>3334</v>
       </c>
       <c r="D3" t="s">
-        <v>3323</v>
+        <v>4621</v>
       </c>
       <c r="E3" t="s">
-        <v>3324</v>
+        <v>4622</v>
       </c>
       <c r="F3" t="s">
-        <v>3325</v>
+        <v>4623</v>
       </c>
       <c r="G3" t="s">
-        <v>3326</v>
+        <v>4624</v>
       </c>
       <c r="H3" t="s">
         <v>3327</v>
       </c>
       <c r="I3" t="s">
-        <v>3328</v>
+        <v>4625</v>
       </c>
       <c r="J3" t="s">
-        <v>3329</v>
+        <v>4626</v>
       </c>
       <c r="K3" t="s">
-        <v>3330</v>
+        <v>4627</v>
       </c>
       <c r="L3" t="s">
-        <v>3331</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -47915,31 +48008,31 @@
         <v>3337</v>
       </c>
       <c r="D4" t="s">
-        <v>3323</v>
+        <v>4629</v>
       </c>
       <c r="E4" t="s">
-        <v>3324</v>
+        <v>4630</v>
       </c>
       <c r="F4" t="s">
-        <v>3325</v>
+        <v>4631</v>
       </c>
       <c r="G4" t="s">
-        <v>3326</v>
+        <v>4632</v>
       </c>
       <c r="H4" t="s">
         <v>3327</v>
       </c>
       <c r="I4" t="s">
-        <v>3328</v>
+        <v>4633</v>
       </c>
       <c r="J4" t="s">
-        <v>3329</v>
+        <v>4634</v>
       </c>
       <c r="K4" t="s">
-        <v>3330</v>
+        <v>4635</v>
       </c>
       <c r="L4" t="s">
-        <v>3331</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -47987,7 +48080,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -48906,69 +48999,82 @@
         <v>4604</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" ht="30">
       <c r="A35" s="67" t="s">
         <v>4520</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="B35" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="C35" s="67" t="s">
+        <v>3352</v>
+      </c>
+      <c r="E35" s="67" t="s">
+        <v>4606</v>
+      </c>
+      <c r="F35" s="67" t="s">
+        <v>4607</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>4608</v>
+      </c>
+      <c r="H35" s="67" t="s">
+        <v>4609</v>
+      </c>
+      <c r="I35" s="67" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="30">
       <c r="A36" s="67" t="s">
         <v>4521</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="B36" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>3359</v>
+      </c>
+      <c r="E36" s="67" t="s">
+        <v>4611</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>4612</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>4613</v>
+      </c>
+      <c r="H36" s="67" t="s">
+        <v>4614</v>
+      </c>
+      <c r="I36" s="67" t="s">
+        <v>4615</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="30">
       <c r="A37" s="67" t="s">
         <v>4522</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="67" t="s">
-        <v>4523</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="67" t="s">
-        <v>4524</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="67" t="s">
-        <v>4525</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="67" t="s">
-        <v>4526</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="67" t="s">
-        <v>4527</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="67" t="s">
-        <v>4528</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="67" t="s">
-        <v>4529</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="67" t="s">
-        <v>4530</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="67" t="s">
-        <v>4531</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="67" t="s">
-        <v>4532</v>
+      <c r="B37" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="C37" s="67" t="s">
+        <v>3366</v>
+      </c>
+      <c r="E37" s="67" t="s">
+        <v>4616</v>
+      </c>
+      <c r="F37" s="67" t="s">
+        <v>4617</v>
+      </c>
+      <c r="G37" s="67" t="s">
+        <v>4618</v>
+      </c>
+      <c r="H37" s="67" t="s">
+        <v>4619</v>
+      </c>
+      <c r="I37" s="67" t="s">
+        <v>4620</v>
       </c>
     </row>
   </sheetData>
